--- a/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0009.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0009.xlsx
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Vì đã có những người sở hữu Năng Lực Resonance rồi...</t>
+          <t>Vì đã có những người sở hữu Năng Lực Cộng Hưởng rồi...</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Humans đã phải chịu đựng biết bao đau khổ trước bọn Suan'nis, với vẻ ngoài đáng sợ, Khả Năng Resonance mạnh mẽ và bản năng thú dữ...</t>
+          <t>Con người đã phải chịu đựng biết bao đau khổ trước bọn Suan'nis, với vẻ ngoài đáng sợ, Khả Năng Cộng Hưởng mạnh mẽ và bản năng thú dữ...</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Yinlin đưa cậu đến gặp Người Chế Tạo Búp Bê, nhưng vẫn giữ vẻ thù địch vì con bọ mà hắn cấy vào người cậu. Qua một tấm vách bí mật, cô tiết lộ nhà máy này sản xuất những con rối được thiết kế để kích hoạt Quá Tải cho Fractsidus, đổi lại là tài nguyên. Cô cần sự giúp đỡ của cậu để thu thập bằng chứng về sự dính líu của Người Chế Tạo Búp Bê trong vụ này.</t>
+          <t>Ân Lâm đưa cậu đến gặp Người Chế Tạo Búp Bê, nhưng vẫn giữ vẻ thù địch vì con bọ mà hắn cấy vào người cậu. Qua một tấm vách bí mật, cô tiết lộ nhà máy này sản xuất những con rối được thiết kế để kích hoạt Quá Tải cho Fractsidus, đổi lại là tài nguyên. Cô cần sự giúp đỡ của cậu để thu thập bằng chứng về sự dính líu của Người Chế Tạo Búp Bê trong vụ này.</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Giờ thì, mục tiêu tiếp theo là...</t>
+          <t>Giờ thì, mục tiêu tiếp theo là…</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Giờ thì, mục tiêu tiếp theo là...</t>
+          <t>Giờ thì, mục tiêu tiếp theo là…</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Hôm nay ta không đánh đâu, nhưng nghiên cứu đối thủ thì chẳng bao giờ thừa. Là một đấu thủ chuyên nghiệp, ngươi phải biết kẻ thù của mình, phải không?</t>
+          <t>Hôm nay tao không đánh đâu, nhưng nghiên cứu đối thủ thì chẳng bao giờ thừa. Là một đấu thủ chuyên nghiệp, mày phải biết kẻ thù của mình, phải không?</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Bí mật tai tiếng nhất của gia tộc Montelli? Có lẽ là... Lady Carlotta thực chất là con của một gia đình Fisalia, nhưng khả năng Resonance của cô đã đưa cô đến với nhà Montelli!</t>
+          <t>Bí mật tai tiếng nhất của gia tộc Montelli? Có lẽ là... Lady Carlotta thực chất là con của một gia đình Fisalia, nhưng khả năng Cộng Hưởng của cô đã đưa cô đến với nhà Montelli!</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Tần số phát ra khi một Resonator mới xuất hiện, sử dụng Forte hoặc kích hoạt Overclock sẽ bị Nexus thu thập và tải lên Tethys.</t>
+          <t>Tần số phát ra khi một Cộng Hưởng Giả mới xuất hiện, sử dụng Forte hoặc kích hoạt Overclock sẽ bị Nexus thu thập và tải lên Tethys.</t>
         </is>
       </c>
     </row>
@@ -2869,23 +2869,23 @@
       <c r="M37" t="inlineStr">
         <is>
           <t>Về sự kiện
-Trong sự kiện, thu thập Nhẫn Ánh Trăng để mở khóa và nhận phần thưởng. Mua các sản phẩm có gắn thẻ &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/Activity31/CumulativeRecharge/Common/T_TempScoreIcon.T_TempScoreIcon,0.5/&gt; trong các mục &lt;color=#ad893a&gt;Được đề xuất - Weekly Subscription, Được đề xuất - Lunite Subscription, Bundles - Special Offers, Outfits - Vehicle Looks, and the Lunite Mua&lt;/color&gt; tại Cửa hàng để nhận Nhẫn Ánh Trăng.
-Khi sự kiện Moonlit Path kết thúc, Nhẫn Ánh Trăng sẽ hết hạn và không được quy đổi sang vật phẩm khác. Sau khi sự kiện kết thúc, phần thưởng chưa nhận sẽ được gửi lại qua thư trong game nếu bạn đăng nhập trong vòng 30 ngày. Nếu không đăng nhập trong 30 ngày, phần thưởng sẽ không được gửi lại. Đừng quên kiểm tra hộp thư trong game nhé.
+Trong sự kiện, thu thập Nhẫn Ánh Trăng để mở khóa và nhận phần thưởng. Mua các sản phẩm có gắn thẻ &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/Activity31/CumulativeRecharge/Common/T_TempScoreIcon.T_TempScoreIcon,0.5/&gt; trong các mục &lt;color=#ad893a&gt;Đề Xuất - Đăng Ký Hàng Tuần, Đề Xuất - Đăng Ký Lunite, Gói Ưu Đãi - Ưu Đãi Đặc Biệt, Trang Phục - Ngoại Hình Xe, và Mua Lunite&lt;/color&gt; tại Cửa Hàng để nhận Nhẫn Ánh Trăng.
+Khi sự kiện Con Đường Ánh Trăng kết thúc, Nhẫn Ánh Trăng sẽ hết hạn và không được quy đổi sang vật phẩm khác. Sau khi sự kiện kết thúc, phần thưởng chưa nhận sẽ được gửi lại qua thư trong game nếu bạn đăng nhập trong vòng 30 ngày. Nếu không đăng nhập trong 30 ngày, phần thưởng sẽ không được gửi lại. Đừng quên kiểm tra hộp thư trong game nhé.
 Điều kiện tham gia
 - Đạt Cấp Liên Minh 5.
-- Hoặc hoàn thành thử thách chiến đấu trong Nhiệm Vụ Chính "Resonance Đầu Tiên".
+- Hoặc hoàn thành thử thách chiến đấu trong Nhiệm Vụ Chính "Cộng Hưởng Đầu Tiên".
 - Hoặc tham gia Sự Kiện Tiến Độ Nhiệm Vụ Chính và tiếp tục Nhiệm Vụ Chính đến một điểm nhất định.
 Quy tắc
 Trong sự kiện, thu thập Nhẫn Ánh Trăng để mở khóa và nhận phần thưởng.
-Đăng nhập và tham gia Moonlit Path để nhận: Thủy Triều Lấp Lánh x1
+Đăng nhập và tham gia Con Đường Ánh Trăng để nhận: Lustrous Tide x1
 Thu thập 30 Nhẫn Ánh Trăng để nhận: Thủy Triều Rạng Rỡ x1
 Thu thập 88 Nhẫn Ánh Trăng để nhận: Phụ Kiện Xe - Vị Cứu Tinh Nhỏ
 Thu thập 198 Nhẫn Ánh Trăng để nhận: Thủy Triều Rèn Luyện x2
-Thu thập 328 Nhẫn Ánh Trăng để nhận: Mẫu Sơn Xe Tùy Chỉnh - Ca Sĩ Vùng Sâu (Bộ đầy đủ gồm: Cánh Trái, Cánh Right, Trước/Sau)
-Thu thập 450 Nhẫn Ánh Trăng để nhận: 5-star Weapon Supply Chest - Vũ Khí Tổng Hợp x1 (Mở để chọn một trong các vũ khí: Laser Shearer, Radiance Cleaver, Phasic Homogenizer, Pulsation Bracer, hoặc Boson Astrolabe)
+Thu thập 328 Nhẫn Ánh Trăng để nhận: Mẫu Sơn Xe Tùy Chỉnh - Ca Sĩ Vùng Sâu (Bộ đầy đủ gồm: Cánh Trái, Cánh Phải, Trước/Sau)
+Thu thập 450 Nhẫn Ánh Trăng để nhận: Rương Cung Cấp Vũ Khí 5 Sao - Vũ Khí Tổng Hợp x1 (Mở để chọn một trong các vũ khí: Laser Shearer, Radiance Cleaver, Phasic Homogenizer, Pulsation Bracer, hoặc Boson Astrolabe)
 Thu thập 680 Nhẫn Ánh Trăng để nhận: Transducer x3
 Thu thập 980 Nhẫn Ánh Trăng để nhận: Neo Tinh Tú Ký Ức x1 (Đổi lấy Shorekeeper, Camellya, hoặc Jinhsi, hoặc Transducer x8)
-Thu thập 1600 Nhẫn Ánh Trăng để nhận: Bộ Trang Phục x1 (Bộ đầy đủ gồm: Hình Đại Diện: Dàn Hợp Xướng Sao, Huy Hiệu: Ân Huệ Của Sao, Phụ Kiện Tùy Chỉnh: Starbright Resonance)
+Thu thập 1600 Nhẫn Ánh Trăng để nhận: Bộ Trang Phục x1 (Bộ đầy đủ gồm: Hình Đại Diện: Dàn Hợp Xướng Sao, Huy Hiệu: Ân Huệ Của Sao, Phụ Kiện Tùy Chỉnh: Cộng Hưởng Sao Sáng)
 Lưu ý
 - Nếu bạn mua hàng qua bất kỳ kênh nào không phải trong game, như trung tâm nạp tiền trên trang web chính thức, vui lòng đăng nhập vào game khi sự kiện đang diễn ra để nhận đơn hàng và số Nhẫn Ánh Trăng tương ứng. Nếu đăng nhập sau khi sự kiện kết thúc, bạn sẽ không nhận được Nhẫn Ánh Trăng tương ứng.</t>
         </is>
@@ -2972,23 +2972,23 @@
       <c r="M38" t="inlineStr">
         <is>
           <t>Về sự kiện
-Trong sự kiện, thu thập Nhẫn Ánh Trăng để mở khóa và nhận phần thưởng. Mua các sản phẩm có gắn thẻ &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/Activity31/CumulativeRecharge/Common/T_TempScoreIcon.T_TempScoreIcon,0.5/&gt; trong các mục &lt;color=#ad893a&gt;Được đề xuất - Weekly Subscription, Được đề xuất - Lunite Subscription, Bundles - Special Offers, Outfits - Vehicle Looks, and the Lunite Mua&lt;/color&gt; tại Cửa hàng để nhận Nhẫn Ánh Trăng.
-Khi sự kiện Moonlit Path kết thúc, Nhẫn Ánh Trăng sẽ hết hạn và không được quy đổi sang vật phẩm khác. Sau khi sự kiện kết thúc, phần thưởng chưa nhận sẽ được gửi lại qua thư trong game nếu bạn đăng nhập trong vòng 30 ngày. Nếu không đăng nhập trong 30 ngày, phần thưởng sẽ không được gửi lại. Đừng quên kiểm tra hộp thư trong game nhé.
+Trong sự kiện, thu thập Nhẫn Ánh Trăng để mở khóa và nhận phần thưởng. Mua các sản phẩm có gắn thẻ &lt;texture=/Game/Aki/UI/UIResources/UiActivity/Image/Activity31/CumulativeRecharge/Common/T_TempScoreIcon.T_TempScoreIcon,0.5/&gt; trong các mục &lt;color=#ad893a&gt;Đề Xuất - Đăng Ký Hàng Tuần, Đề Xuất - Đăng Ký Lunite, Gói Ưu Đãi - Ưu Đãi Đặc Biệt, Trang Phục - Ngoại Hình Xe, và Mua Lunite&lt;/color&gt; tại Cửa Hàng để nhận Nhẫn Ánh Trăng.
+Khi sự kiện Con Đường Ánh Trăng kết thúc, Nhẫn Ánh Trăng sẽ hết hạn và không được quy đổi sang vật phẩm khác. Sau khi sự kiện kết thúc, phần thưởng chưa nhận sẽ được gửi lại qua thư trong game nếu bạn đăng nhập trong vòng 30 ngày. Nếu không đăng nhập trong 30 ngày, phần thưởng sẽ không được gửi lại. Đừng quên kiểm tra hộp thư trong game nhé.
 Điều kiện tham gia
 - Đạt Cấp Liên Minh 5.
-- Hoặc hoàn thành thử thách chiến đấu trong Nhiệm Vụ Chính "Resonance Đầu Tiên".
+- Hoặc hoàn thành thử thách chiến đấu trong Nhiệm Vụ Chính "Cộng Hưởng Đầu Tiên".
 - Hoặc tham gia Sự Kiện Tiến Độ Nhiệm Vụ Chính và tiếp tục Nhiệm Vụ Chính đến một điểm nhất định.
 Quy tắc
 Trong sự kiện, thu thập Nhẫn Ánh Trăng để mở khóa và nhận phần thưởng.
-Đăng nhập và tham gia Moonlit Path để nhận: Thủy Triều Lấp Lánh x1
+Đăng nhập và tham gia Con Đường Ánh Trăng để nhận: Lustrous Tide x1
 Thu thập 30 Nhẫn Ánh Trăng để nhận: Thủy Triều Rạng Rỡ x1
 Thu thập 88 Nhẫn Ánh Trăng để nhận: Phụ Kiện Xe - Vị Cứu Tinh Nhỏ
 Thu thập 198 Nhẫn Ánh Trăng để nhận: Thủy Triều Rèn Luyện x2
-Thu thập 328 Nhẫn Ánh Trăng để nhận: Mẫu Sơn Xe Tùy Chỉnh - Ca Sĩ Vùng Sâu (Bộ đầy đủ gồm: Cánh Trái, Cánh Right, Trước/Sau)
-Thu thập 450 Nhẫn Ánh Trăng để nhận: 5-star Weapon Supply Chest - Vũ Khí Tổng Hợp x1 (Mở để chọn một trong các vũ khí: Laser Shearer, Radiance Cleaver, Phasic Homogenizer, Pulsation Bracer, hoặc Boson Astrolabe)
+Thu thập 328 Nhẫn Ánh Trăng để nhận: Mẫu Sơn Xe Tùy Chỉnh - Ca Sĩ Vùng Sâu (Bộ đầy đủ gồm: Cánh Trái, Cánh Phải, Trước/Sau)
+Thu thập 450 Nhẫn Ánh Trăng để nhận: Rương Cung Cấp Vũ Khí 5 Sao - Vũ Khí Tổng Hợp x1 (Mở để chọn một trong các vũ khí: Laser Shearer, Radiance Cleaver, Phasic Homogenizer, Pulsation Bracer, hoặc Boson Astrolabe)
 Thu thập 680 Nhẫn Ánh Trăng để nhận: Transducer x3
 Thu thập 980 Nhẫn Ánh Trăng để nhận: Neo Tinh Tú Ký Ức x1 (Đổi lấy Shorekeeper, Camellya, hoặc Jinhsi, hoặc Transducer x8)
-Thu thập 1600 Nhẫn Ánh Trăng để nhận: Bộ Trang Phục x1 (Bộ đầy đủ gồm: Hình Đại Diện: Dàn Hợp Xướng Sao, Huy Hiệu: Ân Huệ Của Sao, Phụ Kiện Tùy Chỉnh: Starbright Resonance)
+Thu thập 1600 Nhẫn Ánh Trăng để nhận: Bộ Trang Phục x1 (Bộ đầy đủ gồm: Hình Đại Diện: Dàn Hợp Xướng Sao, Huy Hiệu: Ân Huệ Của Sao, Phụ Kiện Tùy Chỉnh: Cộng Hưởng Sao Sáng)
 Lưu ý
 - Nếu bạn mua hàng qua bất kỳ kênh nào không phải trong game, như trung tâm nạp tiền trên trang web chính thức, vui lòng đăng nhập vào game khi sự kiện đang diễn ra để nhận đơn hàng và số Nhẫn Ánh Trăng tương ứng. Nếu đăng nhập sau khi sự kiện kết thúc, bạn sẽ không nhận được Nhẫn Ánh Trăng tương ứng.</t>
         </is>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>"Starbright Resonance" đã bị gỡ bỏ</t>
+          <t>"Starbright Resonance" đã được tháo bỏ</t>
         </is>
       </c>
     </row>
@@ -3199,21 +3199,21 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>[Weekly Subscription]
-Weekly Subscription chỉ có thể mua một lần trong mỗi kỳ.
-Weekly Subscription có hiệu lực trong 15 ngày kể từ ngày kích hoạt. Đăng nhập vào những ngày cụ thể trong thời hạn gói để nhận tổng cộng x680 Lunite, x1600 Astrite và x1 Transducer.
+          <t>[Gói Đăng Ký Hàng Tuần]
+Gói Đăng Ký Hàng Tuần chỉ có thể mua một lần trong mỗi kỳ.
+Gói Đăng Ký Hàng Tuần có hiệu lực trong 15 ngày kể từ ngày kích hoạt. Đăng nhập vào những ngày cụ thể trong thời hạn gói để nhận tổng cộng x680 Lunite, x1600 Astrite và x1 Transducer.
 Quy tắc mở khóa phần thưởng:
-- Kích hoạt Weekly Subscription sẽ mở khóa ngay lập tức x680 Lunite và x1 Transducer.
+- Kích hoạt Gói Đăng Ký Hàng Tuần sẽ mở khóa ngay lập tức x680 Lunite và x1 Transducer.
 - Trong thời hạn gói, đăng nhập vào ngày thứ 3 trở đi để mở khóa x800 Astrite.
 - Trong thời hạn gói, đăng nhập vào ngày thứ 7 trở đi để mở khóa x800 Astrite.
-- Rewards chỉ có thể nhận một lần sau khi mở khóa.
-&lt;b&gt;Nếu bạn đã mở khóa nhưng chưa nhận phần thưởng khi Weekly Subscription hết hạn, hãy đăng nhập vào game trong vòng 30 ngày sau khi hết hạn, phần thưởng sẽ được gửi qua thư. Quá 30 ngày, phần thưởng sẽ không được cấp lại. Hãy nhận phần thưởng đúng hạn.&lt;/b&gt;
+- Phần thưởng chỉ có thể nhận một lần sau khi mở khóa.
+&lt;b&gt;Nếu bạn đã mở khóa nhưng chưa nhận phần thưởng khi Gói Đăng Ký Hàng Tuần hết hạn, hãy đăng nhập vào game trong vòng 30 ngày sau khi hết hạn, phần thưởng sẽ được gửi qua thư. Quá 30 ngày, phần thưởng sẽ không được cấp lại. Hãy nhận phần thưởng đúng hạn.&lt;/b&gt;
 [Lưu ý]
-- Weekly Subscription có hiệu lực trong 15 ngày kể từ khi kích hoạt và không bị ảnh hưởng bởi thời gian bán gói.
+- Gói Đăng Ký Hàng Tuần có hiệu lực trong 15 ngày kể từ khi kích hoạt và không bị ảnh hưởng bởi thời gian bán gói.
 Ví dụ: nếu bạn mua và kích hoạt gói ba ngày trước khi gói bị gỡ khỏi cửa hàng, bạn vẫn có thể đăng nhập trong 15 ngày để mở khóa và nhận phần thưởng.
 - Đối với giao dịch mua ngoài game (ví dụ: mua trên web), bạn phải kích hoạt gói bằng cách đăng nhập vào game trước khi gói bị gỡ khỏi cửa hàng, thời gian kích hoạt sẽ bắt đầu từ lần đăng nhập đầu tiên sau khi mua.
-- Đối với giao dịch mua ngoài game (ví dụ: mua trên web), &lt;b&gt;nếu bạn chưa đăng nhập vào game trước khi gói bị gỡ khỏi cửa hàng, Weekly Subscription sẽ không thể kích hoạt và bạn sẽ được hoàn lại x750 Lunite.&lt;/b&gt;
-- Trong trường hợp mua nhầm nhiều lần, Weekly Subscription sẽ không chồng chất, và mỗi lần mua thêm sẽ được hoàn lại x750 Lunite.</t>
+- Đối với giao dịch mua ngoài game (ví dụ: mua trên web), &lt;b&gt;nếu bạn chưa đăng nhập vào game trước khi gói bị gỡ khỏi cửa hàng, Gói Đăng Ký Hàng Tuần sẽ không thể kích hoạt và bạn sẽ được hoàn lại x750 Lunite.&lt;/b&gt;
+- Trong trường hợp mua nhầm nhiều lần, Gói Đăng Ký Hàng Tuần sẽ không chồng chất, và mỗi lần mua thêm sẽ được hoàn lại x750 Lunite.</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Kích hoạt Buff của Lifer</t>
+          <t>Kích hoạt Buff Người Sống</t>
         </is>
       </c>
     </row>
@@ -3343,7 +3343,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Kích hoạt Skybox Nhiệm vụ</t>
+          <t>Kích hoạt Skybox nhiệm vụ</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Mục tiêu Bắn</t>
+          <t>Bia Bắn</t>
         </is>
       </c>
     </row>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Kích hoạt Trạng thái</t>
+          <t>Kích hoạt Trạng Thái</t>
         </is>
       </c>
     </row>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Bệ Stand Mục Tiêu</t>
+          <t>Bệ Đứng Mục Tiêu</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Trigger</t>
+          <t>Kích hoạt</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Chọn Buff</t>
+          <t>Chọn Hiệu Ứng Tăng Cường</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Resonance Beacon</t>
+          <t>Điểm Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Resonance Cord</t>
+          <t>Dây Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Crystal Cluster Resonance</t>
+          <t>Cộng Hưởng Cụm Pha Lê</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Disable Hiệu Ứng Buff Của Lifer</t>
+          <t>Vô Hiệu Hóa Hiệu Ứng Tăng Cường Của Lifer</t>
         </is>
       </c>
     </row>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Mục tiêu Bắn</t>
+          <t>Bia Bắn</t>
         </is>
       </c>
     </row>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Combo Kẻ địch 1</t>
+          <t>Hồi chiêu liên hoàn 1 của địch</t>
         </is>
       </c>
     </row>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Vị trí Mục tiêu 2</t>
+          <t>Vị Trí Mục Tiêu 2</t>
         </is>
       </c>
     </row>
@@ -4578,7 +4578,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Thu hồi những con rối.</t>
+          <t>Lấy lại những con rối.</t>
         </is>
       </c>
     </row>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Kích hoạt Thông tin Gondola</t>
+          <t>Kích hoạt truyền thuyết Gondola</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Kích hoạt Di động</t>
+          <t>Cò Súng Cơ Động</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Khôi phục Wish Tag II</t>
+          <t>Khôi phục Thẻ Ước II</t>
         </is>
       </c>
     </row>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Buff ẩn</t>
+          <t>Tăng cường ẩn</t>
         </is>
       </c>
     </row>
@@ -5033,7 +5033,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Resonance Cord Nightmare Nest</t>
+          <t>Dây Cộng Hưởng Tổ Ác Mộng</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Nhận Hiệu Ứng Buff</t>
+          <t>Nhận Hiệu Ứng Tăng Cường</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Restore</t>
+          <t>Hồi phục</t>
         </is>
       </c>
     </row>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Vị trí Mục tiêu 1</t>
+          <t>Vị Trí Mục Tiêu 1</t>
         </is>
       </c>
     </row>
@@ -5293,7 +5293,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Khôi phục Wish Tag I</t>
+          <t>Khôi phục Thẻ Ước I</t>
         </is>
       </c>
     </row>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Resonance Nexus</t>
+          <t>Mạng Lưới Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -5423,7 +5423,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Khôi Phục Wish Tag III</t>
+          <t>Khôi Phục Thẻ Nguyện Ước III</t>
         </is>
       </c>
     </row>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 5 đòn tấn công liên tiếp, gây &lt;color=#1891e7ff&gt;Glacio DMG&lt;/color&gt;. Khi thực hiện Basic Attack V, nhận 1 tầng "Thanh Tịnh".</t>
+          <t>Thực hiện tối đa 5 đòn tấn công liên tiếp, gây &lt;color=#1891e7ff&gt;Sát Thương Glacio&lt;/color&gt;. Khi thực hiện Đòn Basic Attack V, nhận 1 tầng "Thanh Tịnh".</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Sanhua: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Sanhua: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Giữ &lt;color=#f4d582&gt;Heavy Attack&lt;/color&gt; và thả khi con trỏ nằm trong vùng "Đóng Băng" để tung ra &lt;color=#d4bf5f&gt;Heavy Attack: Detonate&lt;/color&gt;, gây &lt;color=#1891e7ff&gt;Glacio DMG&lt;/color&gt;.</t>
+          <t>Giữ &lt;color=#f4d582&gt;Đòn Tấn Công Mạnh&lt;/color&gt; và thả khi con trỏ nằm trong vùng "Đóng Băng" để tung ra &lt;color=#d4bf5f&gt;Đòn Tấn Công Mạnh: Kích Nổ&lt;/color&gt;, gây &lt;color=#1891e7ff&gt;Sát Thương Glacio&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Sanhua: Hướng dẫn &lt;color=#f4d582&gt;Heavy Attack&lt;/color&gt; &lt;color=#d4bf5f&gt;Detonate&lt;/color&gt;</t>
+          <t>Sanhua: Hướng dẫn &lt;color=#f4d582&gt;Tấn Công Mạnh&lt;/color&gt; &lt;color=#d4bf5f&gt;Kích Nổ&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để thực hiện Đòn Lao Xuống từ trên không, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để thực hiện Đòn Lao Xuống từ trên không, gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -5813,7 +5813,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;. Để lại 1 "Ice Prism". Nhận 1 tầng "Sáng Suốt".</t>
+          <t>Gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;. Để lại 1 "Lăng Kính Băng". Nhận 1 tầng "Sáng Suốt".</t>
         </is>
       </c>
     </row>
@@ -5878,7 +5878,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Sanhua: Hướng dẫn Resonance Skill</t>
+          <t>Sanhua: Resonance Skill Tutorial</t>
         </is>
       </c>
     </row>
@@ -5943,7 +5943,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Gây &lt;color=#1891e7ff&gt;Glacio DMG&lt;/color&gt; và tạo ra 1 "Glacier". Đồng thời, nhận 2 tầng "Thanh Minh".</t>
+          <t>Gây &lt;color=#1891e7ff&gt;DMG Glacio&lt;/color&gt; và tạo ra 1 "Băng Hà". Đồng thời, nhận 2 tầng "Thanh Minh".</t>
         </is>
       </c>
     </row>
@@ -6073,7 +6073,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Sanhua: Hướng dẫn Resonance Liberation</t>
+          <t>Sanhua: Resonance Liberation Tutorial</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Đòn &lt;color=#f4d582&gt;Heavy Attack: Detonate&lt;/color&gt; sẽ kích nổ "Ice Thorn", "Ice Prism" và "Sông Băng" trên đường tấn công, gây &lt;color=#1891e7ff&gt;Glacio DMG&lt;/color&gt;.</t>
+          <t>Đòn &lt;color=#f4d582&gt;Heavy Attack: Kích Nổ&lt;/color&gt; sẽ kích nổ "Gai Băng", "Lăng Kính Băng" và "Sông Băng" trên đường tấn công, gây &lt;color=#1891e7ff&gt;Sát Thương Glacio&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -6203,7 +6203,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Sanhua: Hướng dẫn Forte Circuit &lt;color=#d4bf5f&gt;Ice Burst&lt;/color&gt;</t>
+          <t>Sanhua: Hướng dẫn Forte Circuit &lt;color=#d4bf5f&gt;Vụ Nổ Băng&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -6268,7 +6268,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -6333,7 +6333,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Ra lệnh cho You'tan thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=#1891e7ff&gt;Glacio DMG&lt;/color&gt;.</t>
+          <t>Ra lệnh cho You'tan thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=#1891e7ff&gt;Sát Thương Glacio&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Baizhi: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Baizhi: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Liên tục tiêu hao Stamina và kéo You'tan để xoay liên tục tấn công các mục tiêu xung quanh, gây &lt;color=#1891e7ff&gt;Glacio damage&lt;/color&gt;. Có thể điều khiển You'tan di chuyển trong Heavy Attack.</t>
+          <t>Liên tục tiêu hao Thể Lực và kéo You'tan để xoay liên tục tấn công các mục tiêu xung quanh, gây &lt;color=#1891e7ff&gt;sát thương Glacio&lt;/color&gt;. Có thể điều khiển You'tan di chuyển trong Đòn Tấn Công Mạnh.</t>
         </is>
       </c>
     </row>
@@ -6528,7 +6528,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Baizhi: &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt;</t>
+          <t>Baizhi: &lt;color=#d4bf5f&gt;Hướng dẫn Tấn Công Mạnh&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -6593,7 +6593,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để triệu hồi You'tan thực hiện Đòn Lao Xuống Trên Không, gây &lt;color=#1891e7ff&gt;Glacio DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để triệu hồi You'tan thực hiện Tấn Công Lao Xuống Trên Không, gây &lt;color=#1891e7ff&gt;Sát Thương Glacio&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -6658,7 +6658,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Triệu hồi You'tan gây &lt;color=#1891e7ff&gt;Glacio DMG&lt;/color&gt; và phục hồi HP cho tất cả Resonator trong đội gần đó.</t>
+          <t>Triệu hồi You'tan gây &lt;color=#1891e7ff&gt;Sát Thương Glacio&lt;/color&gt; và phục hồi HP cho tất cả Cộng Hưởng Giả trong đội gần đó.</t>
         </is>
       </c>
     </row>
@@ -6723,7 +6723,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Baizhi: Hướng dẫn Resonance Skill</t>
+          <t>Baizhi: Resonance Skill Tutorial</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6788,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Nhận 1 Điểm Concentration khi &lt;color=Highlight&gt;Basic Attacks&lt;/color&gt; trúng mục tiêu. Dùng &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; hoặc Resonance Skill &lt;color=Highlight&gt;Emergency Plan&lt;/color&gt; để tiêu hao toàn bộ Điểm Concentration và hồi phục HP thêm 1 lần cho mỗi Điểm Concentration tiêu hao. Hiệu ứng hồi phục diễn ra mỗi 2 giây.</t>
+          <t>Nhận 1 Điểm Tập Trung khi &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt; trúng mục tiêu. Dùng &lt;color=Highlight&gt;Đòn Heavy Attack&lt;/color&gt; hoặc Resonance Skill &lt;color=Highlight&gt;Kế Hoạch Khẩn Cấp&lt;/color&gt; để tiêu hao toàn bộ Điểm Tập Trung và hồi phục HP thêm 1 lần cho mỗi Điểm Tập Trung tiêu hao. Hiệu ứng hồi phục diễn ra mỗi 2 giây.</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Baizhi: Hướng dẫn Forte Circuit &lt;color=#d4bf5f&gt;Concentration&lt;/color&gt;</t>
+          <t>Baizhi: Hướng dẫn Forte Circuit &lt;color=#d4bf5f&gt;Tập Trung&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Triệu hồi You'tan để lập tức hồi HP cho tất cả Resonator trong đội gần đó và liên tiếp tạo ra 4 &lt;color=Highlight&gt;Remnant Entities&lt;/color&gt;. Thực Thể Tàn Dư sẽ đi theo Resonator đang hoạt động trong đội, tự động tấn công mục tiêu mỗi 2,5 giây, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; khi trúng đích và hồi HP cho tất cả Resonator trong đội gần đó trong phạm vi tấn công.</t>
+          <t>Triệu hồi You'tan để lập tức hồi HP cho tất cả Cộng Hưởng Giả trong đội gần đó và liên tiếp tạo ra 4 &lt;color=Highlight&gt;Thực Thể Tàn Dư&lt;/color&gt;. Thực Thể Tàn Dư sẽ đi theo Cộng Hưởng Giả đang hoạt động trong đội, tự động tấn công mục tiêu mỗi 2,5 giây, gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; khi trúng đích và hồi HP cho tất cả Cộng Hưởng Giả trong đội gần đó trong phạm vi tấn công.</t>
         </is>
       </c>
     </row>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Baizhi: Hướng dẫn Resonance Liberation</t>
+          <t>Baizhi: Resonance Liberation Tutorial</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 5 đòn tấn công, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.</t>
+          <t>Thực hiện tối đa 5 đòn tấn công, gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -7308,7 +7308,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để thực hiện Đòn Lao Xuống từ trên không, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để thực hiện Đòn Lao Xuống từ trên không, gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Tiêu hao STA và gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;. Khi Lion's Spirit chưa đầy, thực hiện &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; sau &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; để tung &lt;color=Highlight&gt;Tail Strike&lt;/color&gt;, tấn công mục tiêu và gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA và gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;. Khi Tinh Thần Sư Tử chưa đầy, thực hiện &lt;color=Highlight&gt;Đòn Cơ Bản&lt;/color&gt; sau &lt;color=Highlight&gt;Đòn Nặng&lt;/color&gt; để tung &lt;color=Highlight&gt;Đòn Quất Đuôi&lt;/color&gt;, tấn công mục tiêu và gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -7503,7 +7503,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Skill để tấn công mục tiêu, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.</t>
+          <t>Kích hoạt Resonance Skill để tấn công mục tiêu, gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -7568,7 +7568,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Lingyang: Hướng dẫn Resonance Skill</t>
+          <t>Lingyang: Resonance Skill Tutorial</t>
         </is>
       </c>
     </row>
@@ -7633,7 +7633,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Basic Attack 3, 4, or 5&lt;/color&gt; trúng mục tiêu, Resonance Skill &lt;color=Highlight&gt;Ancient Arts&lt;/color&gt; sẽ được thay thế bằng Resonance Skill &lt;color=Highlight&gt;Furious Punches&lt;/color&gt;. Khi sử dụng Resonance Skill &lt;color=Highlight&gt;Furious Punches&lt;/color&gt;, bạn sẽ nhận được Lion's Spirit. &lt;color=Highlight&gt;Furious Punches&lt;/color&gt; không làm reset chu kỳ Basic Attack.</t>
+          <t>Khi &lt;color=Highlight&gt;Đòn Basic Attack 3, 4 hoặc 5&lt;/color&gt; trúng mục tiêu, Resonance Skill &lt;color=Highlight&gt;Nghệ Thuật Cổ Xưa&lt;/color&gt; sẽ được thay thế bằng Resonance Skill &lt;color=Highlight&gt;Đòn Đấm Cuồng Nộ&lt;/color&gt;. Khi sử dụng Resonance Skill &lt;color=Highlight&gt;Đòn Đấm Cuồng Nộ&lt;/color&gt;, bạn sẽ nhận được Tinh Thần Sư Tử. &lt;color=Highlight&gt;Đòn Đấm Cuồng Nộ&lt;/color&gt; không làm reset chu kỳ Đòn Basic Attack.</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Lingyang: Hướng dẫn Resonance Skill &lt;color=Highlight&gt;Furious Punches&lt;/color&gt;</t>
+          <t>Lingyang: Hướng dẫn Resonance Skill &lt;color=Highlight&gt;Đòn Đánh Cuồng Nộ&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Basic Attack 3, 4, or 5&lt;/color&gt; trúng mục tiêu, Resonance Skill &lt;color=Highlight&gt;Ancient Arts&lt;/color&gt; sẽ được thay thế bằng Resonance Skill &lt;color=Highlight&gt;Furious Punches&lt;/color&gt;. Khi sử dụng Resonance Skill &lt;color=Highlight&gt;Furious Punches&lt;/color&gt;, bạn sẽ nhận được Lion's Spirit.</t>
+          <t>Khi &lt;color=Highlight&gt;Đòn Basic Attack 3, 4 hoặc 5&lt;/color&gt; trúng mục tiêu, Resonance Skill &lt;color=Highlight&gt;Nghệ Thuật Cổ Xưa&lt;/color&gt; sẽ được thay thế bằng Resonance Skill &lt;color=Highlight&gt;Đòn Đấm Cuồng Nộ&lt;/color&gt;. Khi sử dụng Resonance Skill &lt;color=Highlight&gt;Đòn Đấm Cuồng Nộ&lt;/color&gt;, bạn sẽ nhận được Tinh Thần Sư Tử.</t>
         </is>
       </c>
     </row>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Làm đầy Forte Gauge</t>
+          <t>Nạp Đầy Thanh Forte</t>
         </is>
       </c>
     </row>
@@ -7893,7 +7893,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Kỹ năng Được Tăng cường</t>
+          <t>Kỹ Năng Nâng Cao</t>
         </is>
       </c>
     </row>
@@ -7958,7 +7958,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Khi Thanh Lion's Spirit đầy, sử dụng &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Glorious Plunge&lt;/color&gt;, tấn công mục tiêu, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;, và bước vào trạng thái &lt;color=Highlight&gt;Striding Lion&lt;/color&gt;, có thể tấn công trên không. Khi Thanh Lion's Spirit chưa đầy, sử dụng &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; sau &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Tail Strike&lt;/color&gt;, tấn công mục tiêu, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.</t>
+          <t>Khi Thanh Tinh Thần Sư Tử đầy, sử dụng &lt;color=Highlight&gt;Đòn Heavy Attack&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Lao Xuống Huy Hoàng&lt;/color&gt;, tấn công mục tiêu, gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;, và bước vào trạng thái &lt;color=Highlight&gt;Sư Tử Tiến Bước&lt;/color&gt;, có thể tấn công trên không. Khi Thanh Tinh Thần Sư Tử chưa đầy, sử dụng &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt; sau &lt;color=Highlight&gt;Đòn Heavy Attack&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Vụt Đuôi&lt;/color&gt;, tấn công mục tiêu, gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -8088,7 +8088,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Tấn công mục tiêu, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; và nhận phước lành &lt;color=Highlight&gt;Lion's Vigor&lt;/color&gt;. Trong thời gian Lion's Vigor, thời gian của Forte Circuit &lt;color=Highlight&gt;Striding Lion&lt;/color&gt; sẽ được kéo dài tối đa 10 giây. Thực hiện &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; sau &lt;color=Highlight&gt;Strive: Lion's Vigor&lt;/color&gt; nếu Lion's Spirit đã đầy để bước vào trạng thái &lt;color=Highlight&gt;Striding Lion&lt;/color&gt;.</t>
+          <t>Tấn công mục tiêu, gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; và nhận phước lành &lt;color=Highlight&gt;Sức Mạnh Sư Tử&lt;/color&gt;. Trong thời gian Sức Mạnh Sư Tử, thời gian của Forte Circuit &lt;color=Highlight&gt;Sư Tử Bước Nhanh&lt;/color&gt; sẽ được kéo dài tối đa 10 giây. Thực hiện &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt; sau &lt;color=Highlight&gt;Nỗ Lực: Sức Mạnh Sư Tử&lt;/color&gt; nếu Linh Hồn Sư Tử đã đầy để bước vào trạng thái &lt;color=Highlight&gt;Sư Tử Bước Nhanh&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -8218,7 +8218,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Nạp đạn và thực hiện tối đa 4 phát bắn liên tiếp, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Nạp đạn và thực hiện tối đa 4 phát bắn liên tiếp, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -8283,7 +8283,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Chixia: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Chixia: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8348,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Dồn tinh thần và thực hiện bắn liên tiếp tốc độ cao vào mục tiêu, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Dồn tinh thần và thực hiện bắn liên tiếp tốc độ cao vào mục tiêu, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Chixia: Hướng dẫn Resonance Skill</t>
+          <t>Chixia: Resonance Skill Tutorial</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -8543,7 +8543,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Giữ &lt;color=#f4d582&gt;Resonance Skill: Whizzing Fight Spirit&lt;/color&gt; để vào trạng thái bắn "DAKA DAKA!".</t>
+          <t>Giữ &lt;color=#f4d582&gt;Resonance Skill: Tinh Thần Chiến Đấu Vèo Vèo&lt;/color&gt; để vào trạng thái bắn "DAKA DAKA!".</t>
         </is>
       </c>
     </row>
@@ -8673,7 +8673,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -8741,8 +8741,8 @@
       <c r="M126" t="inlineStr">
         <is>
           <t>Trong trạng thái "DAKA DAKA!": 
-Tiêu hao liên tục "Thermobaric Bullets" để tấn công mục tiêu, gây &lt;color=#e15226ff&gt;Fusion DMG&lt;/color&gt;;
-Khi "Thermobaric Bullets" cạn kiệt, thoát khỏi trạng thái "DAKA DAKA!".</t>
+Tiêu hao liên tục "Đạn Nhiệt Áp" để tấn công mục tiêu, gây &lt;color=#e15226ff&gt;Sát Thương Fusion&lt;/color&gt;;
+Khi "Đạn Nhiệt Áp" cạn kiệt, thoát khỏi trạng thái "DAKA DAKA!".</t>
         </is>
       </c>
     </row>
@@ -8807,7 +8807,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Chixia: Hướng dẫn Forte Circuit &lt;color=#d4bf5f&gt;Heroic Bullets&lt;/color&gt;</t>
+          <t>Chixia: Hướng dẫn Forte Circuit &lt;color=#d4bf5f&gt;Đạn Anh Hùng&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -8872,7 +8872,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -8938,8 +8938,8 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Trong trạng thái bắn "DAKA DAKA!", nhấn Basic Attack để bắn 1 phát, gây &lt;color=#e15226ff&gt;Fusion DMG&lt;/color&gt;, sau đó thoát khỏi trạng thái bắn "DAKA DAKA!".
-Nếu nhấn Basic Attack khi đã tiêu thụ 30 "Thermobaric Bullets", sẽ bắn 1 &lt;color=#f4d582&gt;Boom Boom&lt;/color&gt; trước khi thoát khỏi trạng thái bắn "DAKA DAKA!".</t>
+          <t>Trong trạng thái bắn "DAKA DAKA!", nhấn Basic Attack để bắn 1 phát, gây &lt;color=#e15226ff&gt;Sát Thương Fusion&lt;/color&gt;, sau đó thoát khỏi trạng thái bắn "DAKA DAKA!".
+Nếu nhấn Basic Attack khi đã tiêu thụ 30 "Đạn Nhiệt Áp", sẽ bắn 1 &lt;color=#f4d582&gt;Boom Boom&lt;/color&gt; trước khi thoát khỏi trạng thái bắn "DAKA DAKA!".</t>
         </is>
       </c>
     </row>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Chixia: Hướng dẫn Forte Circuit &lt;color=#f4d582&gt;Boom Boom&lt;/color&gt;</t>
+          <t>Chixia: Hướng dẫn Forte Circuit &lt;color=#f4d582&gt;Bùm Bùm&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -9071,7 +9071,7 @@
       <c r="M131" t="inlineStr">
         <is>
           <t>Giữ Basic Attack để vào chế độ ngắm bắn, tăng sức mạnh cho phát đạn.
-Đòn tấn công sau khi tích đủ sẽ gây &lt;color=#e15226ff&gt;Fusion DMG&lt;/color&gt; và tạo Thermobaric Bullets khi trúng mục tiêu.</t>
+Đòn tấn công sau khi tích đủ sẽ gây &lt;color=#e15226ff&gt;Sát Thương Fusion&lt;/color&gt; và tạo Đạn Nhiệt Áp khi trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -9136,7 +9136,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Chixia: &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt;</t>
+          <t>Chixia: &lt;color=#d4bf5f&gt;Hướng dẫn Tấn Công Mạnh&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -9203,7 +9203,7 @@
       <c r="M133" t="inlineStr">
         <is>
           <t>Giữ Basic Attack để vào chế độ ngắm bắn, tăng sức mạnh cho phát đạn.
-Đòn tấn công sau khi tích đủ sẽ gây &lt;color=#e15226ff&gt;Fusion DMG&lt;/color&gt; và tạo Thermobaric Bullets khi trúng mục tiêu.</t>
+Đòn tấn công sau khi tích đủ sẽ gây &lt;color=#e15226ff&gt;Sát Thương Fusion&lt;/color&gt; và tạo Đạn Nhiệt Áp khi trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Chixia: &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt;</t>
+          <t>Chixia: &lt;color=#d4bf5f&gt;Hướng dẫn Tấn Công Mạnh&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -9333,7 +9333,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Tiêu hao STA và liên tục bắn vào mục tiêu trên không, gây &lt;color=#e15226ff&gt;Fusion DMG&lt;/color&gt;, đồng thời kích hoạt "Thermobaric Bullets" khi trúng đích.</t>
+          <t>Tiêu hao STA và liên tục bắn vào mục tiêu trên không, gây &lt;color=#e15226ff&gt;Sát Thương Fusion&lt;/color&gt;, đồng thời kích hoạt "Đạn Nhiệt Áp" khi trúng đích.</t>
         </is>
       </c>
     </row>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Bắn nhanh vào các mục tiêu gần đó, gây &lt;color=#e15226ff&gt;Fusion DMG&lt;/color&gt;, và nhận "Thermobaric Bullets".</t>
+          <t>Bắn nhanh vào các mục tiêu gần đó, gây &lt;color=#e15226ff&gt;Sát Thương Fusion&lt;/color&gt;, và nhận "Đạn Nhiệt Áp".</t>
         </is>
       </c>
     </row>
@@ -9463,7 +9463,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Chixia: Hướng dẫn Resonance Liberation</t>
+          <t>Chixia: Resonance Liberation Tutorial</t>
         </is>
       </c>
     </row>
@@ -9528,7 +9528,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Summon Woolies thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=#e15226ff&gt;Fusion DMG&lt;/color&gt;. Sau &lt;color=#f4d582&gt;Basic Attack IV&lt;/color&gt;, Points Giận Dữ sẽ xuất hiện quanh Encore. Sử dụng &lt;color=#f4d582&gt;Basic Attack&lt;/color&gt; ngay để tung thêm 1 đòn tấn công, gây &lt;color=#e15226ff&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Triệu hồi Woolies thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=#e15226ff&gt;Sát Thương Fusion&lt;/color&gt;. Sau &lt;color=#f4d582&gt;Đòn Cơ Bản IV&lt;/color&gt;, Điểm Giận Dữ sẽ xuất hiện quanh Encore. Sử dụng &lt;color=#f4d582&gt;Đòn Cơ Bản&lt;/color&gt; ngay để tung thêm 1 đòn tấn công, gây &lt;color=#e15226ff&gt;Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9658,7 +9658,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Tiêu hao Thể Lực và ra lệnh cho Woolies tấn công mục tiêu, gây &lt;color=#e15226ff&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA và ra lệnh cho Woolies tấn công mục tiêu, gây &lt;color=#e15226ff&gt;Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Encore: Hướng dẫn &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt;</t>
+          <t>Encore: Hướng dẫn &lt;color=#d4bf5f&gt;Tấn Công Mạnh&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để lao từ trên không xuống, gây &lt;color=#e15226ff&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để lao từ trên không xuống, gây &lt;color=#e15226ff&gt;Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9854,8 +9854,8 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Summon Cloudy và Cosmos, rồi tấn công mục tiêu bằng tia nhiệt độ cao, gây &lt;color=#e15226ff&gt;Fusion DMG&lt;/color&gt;.
-Sau khi sử dụng &lt;color=#f4d582&gt;Flaming Woolies&lt;/color&gt;, Points Tức Giận sẽ xuất hiện quanh Encore. Hãy dùng &lt;color=#f4d582&gt;Flaming Woolies&lt;/color&gt; một lần nữa để thực hiện thêm 1 đòn tấn công, gây &lt;color=#e15226ff&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Triệu hồi Cloudy và Cosmos, rồi tấn công mục tiêu bằng tia nhiệt độ cao, gây &lt;color=#e15226ff&gt;Sát Thương Hỏa&lt;/color&gt;.
+Sau khi sử dụng &lt;color=#f4d582&gt;Cừu Lông Lửa&lt;/color&gt;, Điểm Tức Giận sẽ xuất hiện quanh Encore. Hãy dùng &lt;color=#f4d582&gt;Cừu Lông Lửa&lt;/color&gt; một lần nữa để thực hiện thêm 1 đòn tấn công, gây &lt;color=#e15226ff&gt;Sát Thương Hỏa&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9920,7 +9920,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Encore: Hướng dẫn Resonance Skill</t>
+          <t>Encore: Resonance Skill Tutorial</t>
         </is>
       </c>
     </row>
@@ -9985,7 +9985,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Kỹ năng Phụ</t>
+          <t>Kỹ năng Bổ trợ</t>
         </is>
       </c>
     </row>
@@ -10115,7 +10115,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Khi "Hỗn Loạn" của Encore đạt tối đa, sử dụng &lt;color=#f4d582&gt;Heavy Attack&lt;/color&gt; để bước vào trạng thái Hỗn Loạn và giảm sát thương nhận vào. Sau khi trạng thái Hỗn Loạn kết thúc, Cloudy Frenzy sẽ được kích hoạt, gây &lt;color=#e15226ff&gt;Fusion DMG&lt;/color&gt;, được tính là Sát Thương Resonance Liberation.</t>
+          <t>Khi "Hỗn Loạn" của Encore đạt tối đa, sử dụng &lt;color=#f4d582&gt;Đòn Heavy Attack&lt;/color&gt; để bước vào trạng thái Hỗn Loạn và giảm DMG nhận vào. Sau khi trạng thái Hỗn Loạn kết thúc, Cloudy Frenzy sẽ được kích hoạt, gây &lt;color=#e15226ff&gt;Sát Thương Fusion&lt;/color&gt;, được tính là Sát Thương Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -10180,7 +10180,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Encore: Hướng dẫn Forte Circuit &lt;color=#d4bf5f&gt;Heavy Attack: Cloudy Frenzy&lt;/color&gt;</t>
+          <t>Encore: Hướng dẫn Forte Circuit &lt;color=#d4bf5f&gt;Tấn Công Mạnh: Cuồng Loạn Mây Đen&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -10245,7 +10245,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Encore mất khả năng kiềm chế Cosmos, khiến hắn xuất hiện và tấn công mục tiêu. Encore bước vào trạng thái &lt;color=Highlight&gt;Cosmos Rave&lt;/color&gt;, trong đó Basic Attack, Heavy Attack và Resonance Skill của cô sẽ được thay thế bằng những đòn mới.</t>
+          <t>Encore mất khả năng kiềm chế Cosmos, khiến hắn xuất hiện và tấn công mục tiêu. Encore bước vào trạng thái &lt;color=Highlight&gt;Cosmos Rave&lt;/color&gt;, trong đó Đòn Cơ Bản, Đòn Nặng và Resonance Skill của cô sẽ được thay thế bằng những đòn mới.</t>
         </is>
       </c>
     </row>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Encore: Hướng dẫn Resonance Liberation</t>
+          <t>Encore: Resonance Liberation Tutorial</t>
         </is>
       </c>
     </row>
@@ -10375,7 +10375,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Trong &lt;color=Highlight&gt;Cosmos Rave&lt;/color&gt;, khi "Hỗn Loạn" đầy, dùng &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; để tiêu hao toàn bộ "Hỗn Loạn" và bước vào trạng thái Hỗn Loạn Cosmos. Sau khi trạng thái này kết thúc, toàn bộ "Hỗn Loạn" sẽ bị tiêu hao để thi triển Cosmos: Vỡ Tan, gây &lt;color=#e15226ff&gt;Fusion DMG&lt;/color&gt;, được tính là Sát Thương Resonance Liberation.</t>
+          <t>Trong &lt;color=Highlight&gt;Vũ Điệu Vũ Trụ&lt;/color&gt;, khi "Hỗn Loạn" đầy, dùng &lt;color=Highlight&gt;Đòn Heavy Attack&lt;/color&gt; để tiêu hao toàn bộ "Hỗn Loạn" và bước vào trạng thái Hỗn Loạn Vũ Trụ. Sau khi trạng thái này kết thúc, toàn bộ "Hỗn Loạn" sẽ bị tiêu hao để thi triển Vũ Trụ: Vỡ Tan, gây &lt;color=#e15226ff&gt;Sát Thương Fusion&lt;/color&gt;, được tính là Sát Thương Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -10440,7 +10440,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Encore: Hướng dẫn Forte Circuit &lt;color=#d4bf5f&gt;Heavy Attack: Cosmos Rupture&lt;/color&gt;</t>
+          <t>Encore: Hướng dẫn Forte Circuit &lt;color=#d4bf5f&gt;Tấn Công Mạnh: Vỡ Tan Vũ Trụ&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -10505,7 +10505,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp bằng súng và lửa vào mục tiêu, gây &lt;color=#e15226ff&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp bằng súng và lửa vào mục tiêu, gây &lt;color=#e15226ff&gt;Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -10635,7 +10635,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Phóng một luồng lửa tốc độ cao về phía trước, gây &lt;color=#e15226ff&gt;Fusion DMG&lt;/color&gt;. Trong thời gian sau khi sử dụng &lt;color=#f4d582&gt;Resonance Skill: Passionate Variation&lt;/color&gt;, mỗi đòn Normal Attack trúng mục tiêu sẽ tích thêm "Phiền Toái".</t>
+          <t>Phóng một luồng lửa tốc độ cao về phía trước, gây &lt;color=#e15226ff&gt;Sát Thương Fusion&lt;/color&gt;. Trong thời gian sau khi sử dụng &lt;color=#f4d582&gt;Resonance Skill: Biến Tấu Sôi Động&lt;/color&gt;, mỗi đòn Normal Attack trúng mục tiêu sẽ tích thêm "Phiền Toái".</t>
         </is>
       </c>
     </row>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Mortefi: Hướng dẫn Resonance Skill</t>
+          <t>Mortefi: Resonance Skill Tutorial</t>
         </is>
       </c>
     </row>
@@ -10765,7 +10765,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Khi "Phiền Não" đạt 100, &lt;color=#f4d582&gt;Fury Fugue&lt;/color&gt; sẽ được kích hoạt, tiêu hao toàn bộ "Phiền Não" để phóng tia sét lửa, gây &lt;color=#e15226ff&gt;Fusion DMG&lt;/color&gt;, được tính là Sát Thương Resonance Skill.</t>
+          <t>Khi "Phiền Não" đạt 100, &lt;color=#f4d582&gt;Fury Fugue&lt;/color&gt; sẽ được kích hoạt, tiêu hao toàn bộ "Phiền Não" để phóng tia sét lửa, gây &lt;color=#e15226ff&gt;Sát Thương Fusion&lt;/color&gt;, được tính là Sát Thương Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -10895,7 +10895,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Mortefi: Hướng dẫn Forte Circuit &lt;color=#d4bf5f&gt;Resonance Skill: Fury Fugue&lt;/color&gt;</t>
+          <t>Mortefi: Hướng dẫn Forte Circuit &lt;color=#d4bf5f&gt;Resonance Skill: Khúc Phẫn Nộ&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -10960,7 +10960,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -11027,7 +11027,7 @@
       <c r="M161" t="inlineStr">
         <is>
           <t>Giữ Basic Attack để bắt đầu ngắm bắn.
-Sau khi tích đủ, tấn công và gây &lt;color=#e15226ff&gt;Fusion DMG&lt;/color&gt;.</t>
+Sau khi tích đủ, tấn công và gây &lt;color=#e15226ff&gt;Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       <c r="M162" t="inlineStr">
         <is>
           <t>Giữ Basic Attack để bắt đầu ngắm bắn.
-Sau khi tích đủ, tấn công và gây &lt;color=#e15226ff&gt;Fusion DMG&lt;/color&gt;.</t>
+Sau khi tích đủ, tấn công và gây &lt;color=#e15226ff&gt;Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11224,7 +11224,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Liên tục tiêu hao STA để bắn nhiều phát vào mục tiêu trên không, gây &lt;color=#e15226ff&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Liên tục tiêu hao STA để bắn nhiều phát vào mục tiêu trên không, gây &lt;color=#e15226ff&gt;Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11289,7 +11289,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Gây &lt;color=#e15226ff&gt;Fusion DMG&lt;/color&gt; và áp dụng &lt;color=#f4d582&gt;Burning Rhapsody&lt;/color&gt; lên tất cả Resonators trong đội. Trong trạng thái &lt;color=#d4bf5f&gt;Burning Rhapsody&lt;/color&gt;, đòn Basic Attack và Heavy Attack khi trúng mục tiêu sẽ kích hoạt Attack Phối Hợp, gây &lt;color=#e15226ff&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Gây &lt;color=#e15226ff&gt;DMG Fusion&lt;/color&gt; và áp dụng &lt;color=#f4d582&gt;Khúc Rapsody Cháy Bỏng&lt;/color&gt; lên tất cả Resonator trong đội. Trong trạng thái &lt;color=#d4bf5f&gt;Khúc Rapsody Cháy Bỏng&lt;/color&gt;, đòn Basic Attack và Heavy Attack khi trúng mục tiêu sẽ kích hoạt Tấn Công Phối Hợp, gây &lt;color=#e15226ff&gt;DMG Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Mortefi: Hướng dẫn Resonance Liberation</t>
+          <t>Mortefi: Resonance Liberation Tutorial</t>
         </is>
       </c>
     </row>
@@ -11419,7 +11419,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Bắn tối đa 4 phát liên tiếp bằng súng đôi, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Bắn tối đa 4 phát liên tiếp bằng súng đôi, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11549,7 +11549,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Trong lúc thực hiện &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Dodge để thi triển &lt;color=#d4bf5f&gt;Hellstride&lt;/color&gt; gây một lượng &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; cố định. Kỹ năng này không làm gián đoạn chu kỳ tấn công.</t>
+          <t>Trong lúc thực hiện &lt;color=#d4bf5f&gt;Đòn Cơ Bản&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} né để thi triển &lt;color=#d4bf5f&gt;Hellstride&lt;/color&gt; gây một lượng &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; cố định. Kỹ năng này không làm gián đoạn chu kỳ tấn công.</t>
         </is>
       </c>
     </row>
@@ -11614,7 +11614,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Galbrena: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt; và &lt;color=#d4bf5f&gt;Hellstride&lt;/color&gt; Combo Tutorial</t>
+          <t>Galbrena: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt; và &lt;color=#d4bf5f&gt;Hellstride&lt;/color&gt; Hướng dẫn Combo</t>
         </is>
       </c>
     </row>
@@ -11679,7 +11679,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để tung ra tối đa 3 đòn tấn công liên tiếp, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để tung ra tối đa 3 đòn tấn công liên tiếp, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Trong lúc thực hiện &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Dodge để thi triển &lt;color=#d4bf5f&gt;Hellstride&lt;/color&gt; gây một lượng &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; cố định. Kỹ năng này không làm gián đoạn chu kỳ tấn công.</t>
+          <t>Trong lúc thực hiện &lt;color=#d4bf5f&gt;Đòn Nặng&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} né để thi triển &lt;color=#d4bf5f&gt;Hellstride&lt;/color&gt; gây một lượng &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; cố định. Kỹ năng này không làm gián đoạn chu kỳ tấn công.</t>
         </is>
       </c>
     </row>
@@ -11874,7 +11874,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Galbrena Tutorial Combo &lt;color=#d4bf5f&gt;Heavy Attack - Volley of Death&lt;/color&gt; và &lt;color=#d4bf5f&gt;Hellstride&lt;/color&gt;</t>
+          <t>Galbrena Hướng Dẫn Combo &lt;color=#d4bf5f&gt;Tấn Công Mạnh - Loạt Pháo Tử Thần&lt;/color&gt; và &lt;color=#d4bf5f&gt;Bước Địa Ngục&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Khi ở trên không, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack để tiêu hao Thể Lực và thực hiện Đòn Lao Xuống, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Khi ở trên không, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Đòn Normal Attack để tiêu hao STA và thực hiện Đòn Lao Xuống, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -12004,7 +12004,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Khi ở trên không, giữ Normal Attack để tiêu hao Thể Lực và bắn liên tiếp vào mục tiêu bên dưới, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Khi ở trên không, giữ Đòn Normal Attack để tiêu hao STA và bắn liên tiếp vào mục tiêu bên dưới, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -12069,7 +12069,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Phóng nhanh về phía trước và lộn ngược lại khi trúng mục tiêu, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;. Có thể liên kết với &lt;color=#d4bf5f&gt;Mid-air Attack - Ashfall Barrage&lt;/color&gt; khi Galbrena đang ở trên không.</t>
+          <t>Phóng nhanh về phía trước và lộn ngược lại khi trúng mục tiêu, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;. Có thể liên kết với &lt;color=#d4bf5f&gt;Tấn Công Giữa Không - Loạt Đòn Mưa Tro&lt;/color&gt; khi Galbrena đang ở trên không.</t>
         </is>
       </c>
     </row>
@@ -12134,7 +12134,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Galbrena: &lt;color=#d4bf5f&gt;Resonance Skill - Encroach&lt;/color&gt; và &lt;color=#d4bf5f&gt;Mid-air Attack - Ashfall Barrage&lt;/color&gt; Combo Tutorial Đòn Lao Xuống</t>
+          <t>Galbrena: &lt;color=#d4bf5f&gt;Resonance Skill - Encroach&lt;/color&gt; và &lt;color=#d4bf5f&gt;Tấn Công Giữa Không - Ashfall Barrage&lt;/color&gt; Hướng dẫn Combo Tấn Công Lao Xuống</t>
         </is>
       </c>
     </row>
@@ -12199,7 +12199,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Khi &lt;color=#d4bf5f&gt;Sinflame&lt;/color&gt; đầy, Galbrena sẽ vung cánh chém kẻ địch, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;. Sau khi sử dụng kỹ năng này, Galbrena bước vào trạng thái &lt;color=#d4bf5f&gt;Demon Hypostasis&lt;/color&gt;.</t>
+          <t>Khi &lt;color=#d4bf5f&gt;Sinflame&lt;/color&gt; đầy, Galbrena sẽ vung cánh chém kẻ địch, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;. Sau khi sử dụng kỹ năng này, Galbrena bước vào trạng thái &lt;color=#d4bf5f&gt;Demon Hypostasis&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Khi ở trong &lt;color=#d4bf5f&gt;Demon Hypostasis&lt;/color&gt;, &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt; sẽ được thay thế bằng &lt;color=#d4bf5f&gt;Basic Attack - Seraphic Execution&lt;/color&gt;.</t>
+          <t>Khi ở trong &lt;color=#d4bf5f&gt;Demon Hypostasis&lt;/color&gt;, &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt; sẽ được thay thế bằng &lt;color=#d4bf5f&gt;Basic Attack - Thiên Sứ Hành Quyết&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Trong lúc thực hiện &lt;color=#d4bf5f&gt;Basic Attack - Seraphic Execution&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Dodge để thi triển &lt;color=#d4bf5f&gt;Hellstride&lt;/color&gt; gây một lượng &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; cố định. Kỹ năng này không làm gián đoạn chu kỳ tấn công.</t>
+          <t>Trong lúc thực hiện &lt;color=#d4bf5f&gt;Đòn Cơ Bản - Seraphic Execution&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} né để thi triển &lt;color=#d4bf5f&gt;Hellstride&lt;/color&gt; gây một lượng &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; cố định. Kỹ năng này không làm gián đoạn chu kỳ tấn công.</t>
         </is>
       </c>
     </row>
@@ -12524,7 +12524,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Galbrena: &lt;color=#d4bf5f&gt;Basic Attack - Seraphic Execution&lt;/color&gt; và &lt;color=#d4bf5f&gt;Hellstride&lt;/color&gt; Combo Tutorial</t>
+          <t>Galbrena: &lt;color=#d4bf5f&gt;Basic Attack - Seraphic Execution&lt;/color&gt; và &lt;color=#d4bf5f&gt;Hellstride&lt;/color&gt; Hướng dẫn Combo</t>
         </is>
       </c>
     </row>
@@ -12589,7 +12589,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Tấn công mục tiêu và gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;, tăng 85% Hệ Số Sát Thương cho các đòn tấn công được tăng cường trong 14 giây khi ở trạng thái &lt;color=#d4bf5f&gt;Demon Hypostasis&lt;/color&gt;.</t>
+          <t>Tấn công mục tiêu và gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;, tăng 85% Hệ Số Sát Thương cho các đòn tấn công được tăng cường trong 14 giây khi ở trạng thái &lt;color=#d4bf5f&gt;Demon Hypostasis&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -12719,7 +12719,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -12784,7 +12784,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Mornye: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Mornye: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -12849,7 +12849,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Với &lt;color=#d4bf5f&gt;Rest Mass Energy&lt;/color&gt; tối đa, giữ Normal Attack để gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; và tung Mornye lên không, triệu hồi &lt;color=#d4bf5f&gt;Syntony Field&lt;/color&gt;.</t>
+          <t>Với &lt;color=#d4bf5f&gt;Năng Lượng Khối Lượng Nghỉ&lt;/color&gt; tối đa, giữ Normal Attack để gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; và tung Mornye lên không, triệu hồi &lt;color=#d4bf5f&gt;Trường Cộng Hưởng&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Mornye: &lt;color=#d4bf5f&gt;Heavy Attack - Geopotential Shift&lt;/color&gt;</t>
+          <t>Mornye: &lt;color=#d4bf5f&gt;Hướng dẫn Heavy Attack - Dịch Chuyển Địa Thế&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -12979,7 +12979,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Khi ở trên không, thực hiện tối đa 3 đòn tấn công liên tiếp, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Khi ở trên không, thực hiện tối đa 3 đòn tấn công liên tiếp, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -13044,7 +13044,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Mornye: &lt;color=#d4bf5f&gt;Mid-air Basic Attack&lt;/color&gt;</t>
+          <t>Mornye: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack Giữa Không Trung&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -13109,7 +13109,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Khi ở trên không, triệu hồi Pháo Nổi để tấn công mục tiêu, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; và hồi phục HP cho tất cả Resonators trong đội ở gần.</t>
+          <t>Khi ở trên không, triệu hồi Pháo Nổi để tấn công mục tiêu, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; và hồi phục HP cho tất cả Resonator trong đội ở gần.</t>
         </is>
       </c>
     </row>
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Mornye: &lt;color=#d4bf5f&gt;Resonance Skill&lt;/color&gt;</t>
+          <t>Mornye: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Skill Giữa Không Trung&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -13304,7 +13304,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Khi ở trên không, với &lt;color=#d4bf5f&gt;Relative Momentum&lt;/color&gt; tối đa, giữ Normal Attack để gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; và đánh dấu &lt;color=#d4bf5f&gt;Observation Marker&lt;/color&gt; lên mục tiêu.</t>
+          <t>Khi ở trên không, với &lt;color=#d4bf5f&gt;Động Lượng Tương Đối&lt;/color&gt; tối đa, giữ Đòn Normal Attack để gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; và đánh dấu &lt;color=#d4bf5f&gt;Dấu Hiệu Quan Sát&lt;/color&gt; lên mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -13369,7 +13369,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Mornye: &lt;color=#d4bf5f&gt;Heavy Attack - Inversion&lt;/color&gt;</t>
+          <t>Mornye: &lt;color=#d4bf5f&gt;Hướng dẫn Heavy Attack Giữa Không Trung - Đảo Chiều&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -13434,7 +13434,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -13499,7 +13499,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Mornye: &lt;color=#d4bf5f&gt;Resonance Liberation&lt;/color&gt;</t>
+          <t>Mornye: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Liberation&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -13564,7 +13564,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Khi ở trên không, sử dụng kỹ năng để gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;</t>
+          <t>Khi ở trên không, sử dụng kỹ năng để gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -13629,7 +13629,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Mornye: &lt;color=#d4bf5f&gt;Resonance Liberation&lt;/color&gt;</t>
+          <t>Mornye: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Liberation Giữa Không Trung&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -13694,7 +13694,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 4 đòn tấn công, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.</t>
+          <t>Thực hiện tối đa 4 đòn tấn công, gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -13759,7 +13759,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Calcharo: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Calcharo: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -13824,7 +13824,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để thực hiện Đòn Lao Xuống trên không, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để thực hiện Đòn Lao Xuống trên không, gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -13889,7 +13889,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để tung đòn Heavy Attack, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để tung đòn Heavy Attack, gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -13954,7 +13954,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Calcharo: &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt;</t>
+          <t>Calcharo: &lt;color=#d4bf5f&gt;Hướng dẫn Heavy Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -14019,7 +14019,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Vung kiếm tấn công mục tiêu, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;. Resonance Skill &lt;color=Highlight&gt;Extermination Order&lt;/color&gt; có thể sử dụng tối đa 3 lần liên tiếp nhưng sẽ vào trạng thái Cooldown nếu không sử dụng ngay sau lần trước. Skill này không làm gián đoạn chu kỳ Basic Attack và cộng 1 "Độ Tàn Nhẫn" cho mỗi lần trúng đích.</t>
+          <t>Vung kiếm tấn công mục tiêu, gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;. Resonance Skill &lt;color=Highlight&gt;Lệnh Tiêu Diệt&lt;/color&gt; có thể sử dụng tối đa 3 lần liên tiếp nhưng sẽ vào trạng thái Thời gian hồi nếu không sử dụng ngay sau lần trước. Kỹ năng này không làm gián đoạn chu kỳ Đòn Cơ Bản và cộng 1 "Độ Tàn Nhẫn" cho mỗi lần trúng đích.</t>
         </is>
       </c>
     </row>
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Calcharo: &lt;color=#d4bf5f&gt;Resonance Skill&lt;/color&gt;</t>
+          <t>Calcharo: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Skill&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -14214,7 +14214,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Kỹ năng 2</t>
+          <t>Kỹ Năng 2</t>
         </is>
       </c>
     </row>
@@ -14279,7 +14279,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Kỹ năng 3</t>
+          <t>Kỹ Năng 3</t>
         </is>
       </c>
     </row>
@@ -14344,7 +14344,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Resonance Skill của Calcharo sẽ không làm gián đoạn chuỗi Basic Attack. Mỗi đòn đánh gây Electro DMG và cộng 1 điểm "Tàn Nhẫn".</t>
+          <t>Kỹ năng Cộng Hưởng của Calcharo sẽ không làm gián đoạn chuỗi Đòn Cơ Bản. Mỗi đòn đánh gây Sát Thương Electro và cộng 1 điểm "Tàn Nhẫn".</t>
         </is>
       </c>
     </row>
@@ -14409,7 +14409,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Calcharo: &lt;color=#d4bf5f&gt;Forte Circuit&lt;/color&gt;</t>
+          <t>Calcharo: &lt;color=#d4bf5f&gt;Hướng dẫn Forte Circuit&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -14474,7 +14474,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; sẽ được thay thế bằng Heavy Attack &lt;color=Highlight&gt;"Mercy"&lt;/color&gt; khi Calcharo không ở trạng thái Resonance Liberation &lt;color=Highlight&gt;Deathblade Gear&lt;/color&gt; và có 3 "Lòng Thương Xót". Heavy Attack &lt;color=Highlight&gt;"Mercy"&lt;/color&gt; sẽ tiêu hao toàn bộ "Sự Tàn Nhẫn" để gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.</t>
+          <t>&lt;color=Highlight&gt;Đòn Heavy Attack&lt;/color&gt; sẽ được thay thế bằng Đòn Heavy Attack &lt;color=Highlight&gt;"Lòng Thương Xót"&lt;/color&gt; khi Calcharo không ở trạng thái Resonance Liberation &lt;color=Highlight&gt;Deathblade Gear&lt;/color&gt; và có 3 "Lòng Thương Xót". Đòn Heavy Attack &lt;color=Highlight&gt;"Lòng Thương Xót"&lt;/color&gt; sẽ tiêu hao toàn bộ "Sự Tàn Nhẫn" để gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -14539,7 +14539,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Calcharo: &lt;color=#d4bf5f&gt;Enhanced Heavy Attack&lt;/color&gt;</t>
+          <t>Calcharo: &lt;color=#d4bf5f&gt;Hướng dẫn Heavy Attack Nâng Cao&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -14604,7 +14604,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt; lên các mục tiêu xung quanh và bước vào trạng thái &lt;color=Highlight&gt;Deathblade Gear&lt;/color&gt;. Trong trạng thái &lt;color=Highlight&gt;Deathblade Gear&lt;/color&gt;, &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; và &lt;color=Highlight&gt;Dodge Counter&lt;/color&gt; được tăng cường. Thanh Forte được thay thế bằng "Ý Chí Sát Thủ", và khi "Ý Chí Sát Thủ" đạt 5, &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; sẽ được thay thế bằng &lt;color=Highlight&gt;"Death Messenger"&lt;/color&gt;. &lt;color=Highlight&gt;"Death Messenger"&lt;/color&gt; tiêu hao toàn bộ "Ý Chí Sát Thủ" để gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;. &lt;color=Highlight&gt;Normal Attacks&lt;/color&gt; hồi 1 "Ý Chí Sát Thủ" khi trúng mục tiêu.</t>
+          <t>Gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt; lên các mục tiêu xung quanh và bước vào trạng thái &lt;color=Highlight&gt;Deathblade Gear&lt;/color&gt;. Trong trạng thái &lt;color=Highlight&gt;Deathblade Gear&lt;/color&gt;, &lt;color=Highlight&gt;Đòn Cơ Bản&lt;/color&gt; và &lt;color=Highlight&gt;Dodge Counter Tránh&lt;/color&gt; được tăng cường. Thanh Forte được thay thế bằng "Ý Chí Sát Thủ", và khi "Ý Chí Sát Thủ" đạt 5, &lt;color=Highlight&gt;Đòn Cơ Bản&lt;/color&gt; sẽ được thay thế bằng &lt;color=Highlight&gt;"Death Messenger"&lt;/color&gt;. &lt;color=Highlight&gt;"Death Messenger"&lt;/color&gt; tiêu hao toàn bộ "Ý Chí Sát Thủ" để gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;. &lt;color=Highlight&gt;Đòn tấn công thường&lt;/color&gt; hồi 1 "Ý Chí Sát Thủ" khi trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -14669,7 +14669,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Calcharo: &lt;color=#d4bf5f&gt;Resonance Liberation&lt;/color&gt;</t>
+          <t>Calcharo: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Liberation&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Yinlin điều khiển con rối "Tia Lửa" thực hiện tối đa 4 đòn tấn công, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.</t>
+          <t>Ân Lâm điều khiển con rối "Tia Lửa" thực hiện tối đa 4 đòn tấn công, gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -14799,7 +14799,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Yinlin: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Yinlin: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -14864,7 +14864,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Tiêu hao STA và điều khiển bù nhìn "Zapstring" đâm sầm xuống đất, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA và điều khiển bù nhìn "Zapstring" đâm sầm xuống đất, gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -14929,7 +14929,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Tiêu hao STA và điều khiển bù nhìn "Zapstring" tấn công, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA và điều khiển bù nhìn "Zapstring" tấn công, gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Yinlin: &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt;</t>
+          <t>Yinlin: &lt;color=#d4bf5f&gt;Hướng dẫn Tấn Công Mạnh&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -15059,7 +15059,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Control the puppet "Zapstring" gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt; lên mục tiêu trong phạm vi và kích hoạt &lt;color=Highlight&gt;Execution Mode&lt;/color&gt;. Kích hoạt lại để gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt; một lần nữa và kết thúc &lt;color=Highlight&gt;Execution Mode&lt;/color&gt;.</t>
+          <t>Điều khiển con rối "Zapstring" gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt; lên mục tiêu trong phạm vi và kích hoạt &lt;color=Highlight&gt;Chế Độ Hành Quyết&lt;/color&gt;. Kích hoạt lại để gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt; một lần nữa và kết thúc &lt;color=Highlight&gt;Chế Độ Hành Quyết&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -15124,7 +15124,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Yinlin: &lt;color=#d4bf5f&gt;Resonance Skill&lt;/color&gt;</t>
+          <t>Yinlin: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Skill&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -15189,7 +15189,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Trong &lt;color=Highlight&gt;Execution Mode&lt;/color&gt;, bù nhìn "Zapstring" sẽ liên tục phóng điện và tăng cường &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; cùng &lt;color=Highlight&gt;Dodge Counter&lt;/color&gt; để kích hoạt Vụ Nổ Điện Từ khi trúng đích. Mỗi &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; chỉ kích hoạt một lần, tối đa 4 lần.</t>
+          <t>Trong &lt;color=Highlight&gt;Chế Độ Hành Quyết&lt;/color&gt;, bù nhìn "Zapstring" sẽ liên tục phóng điện và tăng cường &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt; cùng &lt;color=Highlight&gt;Dodge Counter Tránh&lt;/color&gt; để kích hoạt Vụ Nổ Điện Từ khi trúng đích. Mỗi &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt; chỉ kích hoạt một lần, tối đa 4 lần.</t>
         </is>
       </c>
     </row>
@@ -15254,7 +15254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Yinlin: &lt;color=#d4bf5f&gt;Resonance Skill&lt;/color&gt;</t>
+          <t>Yinlin: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Skill&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -15319,7 +15319,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Khi "Points Phán Xét" của Yinlin đạt tối đa, &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; sẽ được thay thế bằng &lt;color=Highlight&gt;Chameleon Cipher&lt;/color&gt;, tiêu hao toàn bộ "Points Phán Xét" và gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt; diện rộng, thay thế "Dấu Hiệu Tội Nhân" bằng "Dấu Hiệu Trừng Phạt" khi trúng mục tiêu. "Sấm Phán Xét" sẽ giáng xuống tất cả mục tiêu mang "Dấu Hiệu Trừng Phạt", gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt; khi mục tiêu bị tấn công. Hiệu ứng này có thể kích hoạt tối đa một lần mỗi giây. Các đòn tấn công sẽ hồi phục "Points Phán Xét" khi trúng mục tiêu.</t>
+          <t>Khi "Điểm Phán Xét" của Yinlin đạt tối đa, &lt;color=Highlight&gt;Đòn Tấn Công Mạnh&lt;/color&gt; sẽ được thay thế bằng &lt;color=Highlight&gt;Mật Mã Tắc Kè&lt;/color&gt;, tiêu hao toàn bộ "Điểm Phán Xét" và gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt; diện rộng, thay thế "Dấu Hiệu Tội Nhân" bằng "Dấu Hiệu Trừng Phạt" khi trúng mục tiêu. "Sấm Phán Xét" sẽ giáng xuống tất cả mục tiêu mang "Dấu Hiệu Trừng Phạt", gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt; khi mục tiêu bị tấn công. Hiệu ứng này có thể kích hoạt tối đa một lần mỗi giây. Các đòn tấn công sẽ hồi phục "Điểm Phán Xét" khi trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -15384,7 +15384,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Yinlin: &lt;color=#d4bf5f&gt;Forte Circuit&lt;/color&gt;</t>
+          <t>Yinlin: &lt;color=#d4bf5f&gt;Hướng dẫn Forte Circuit&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -15449,7 +15449,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt; diện rộng. Khi trúng mục tiêu, một sợi dây "Zapstring" sẽ kết nối con rối với mục tiêu và đánh dấu bằng "Dấu Hiệu Tội Nhân".</t>
+          <t>Gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt; diện rộng. Khi trúng mục tiêu, một sợi dây "Zapstring" sẽ kết nối con rối với mục tiêu và đánh dấu bằng "Dấu Hiệu Tội Nhân".</t>
         </is>
       </c>
     </row>
@@ -15514,7 +15514,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Yinlin: &lt;color=#d4bf5f&gt;Resonance Liberation&lt;/color&gt;</t>
+          <t>Yinlin: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Liberation&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -15579,7 +15579,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 5 đòn tấn công bằng võ thuật mạnh mẽ, gây &lt;color=#9656d8ff&gt;Electro DMG&lt;/color&gt;.</t>
+          <t>Thực hiện tối đa 5 đòn tấn công bằng võ thuật mạnh mẽ, gây &lt;color=#9656d8ff&gt;Sát Thương Electro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -15709,7 +15709,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để lao về phía trước và tấn công mục tiêu, gây &lt;color=#9656d8ff&gt;Electro DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để lao về phía trước và tấn công mục tiêu, gây &lt;color=#9656d8ff&gt;Sát Thương Electro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -15774,7 +15774,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Yuanwu: Hướng dẫn &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt;</t>
+          <t>Yuanwu: Hướng dẫn &lt;color=#d4bf5f&gt;Tấn Công Mạnh&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -15839,7 +15839,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để bật lên và tấn công xuống dưới, gây &lt;color=#9656d8ff&gt;Electro DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để bật lên và tấn công xuống dưới, gây &lt;color=#9656d8ff&gt;Sát Thương Electro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Nhấn Leihuang Master để triệu hồi Lưỡi Tầm Sét, gây &lt;color=#9656d8ff&gt;Electro DMG&lt;/color&gt;.</t>
+          <t>Nhấn Leihuang Master để triệu hồi Lưỡi Tầm Sét, gây &lt;color=#9656d8ff&gt;Sát Thương Electro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -15969,7 +15969,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Yuanwu: Hướng dẫn Resonance Skill - &lt;color=#f4d582&gt;Thunder Wedge&lt;/color&gt;</t>
+          <t>Yuanwu: Hướng dẫn Kỹ năng Cộng Hưởng - &lt;color=#f4d582&gt;Thanh Gươm Sấm Sét&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -16034,7 +16034,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -16099,7 +16099,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Yuanwu triệu hồi một Lưỡi Điện, tạo thành một &lt;color=#f4d582&gt;Thunder Pool&lt;/color&gt; tập trung quanh nó. Khi một Resonator trong đội tấn công mục tiêu trong &lt;color=#f4d582&gt;Thunder Pool&lt;/color&gt;, Lưỡi Điện sẽ thực hiện Attack Phối Hợp, gây &lt;color=#9656d8ff&gt;Electro DMG&lt;/color&gt;.</t>
+          <t>Yuanwu triệu hồi một Lưỡi Điện, tạo thành một &lt;color=#f4d582&gt;Bể Sét&lt;/color&gt; tập trung quanh nó. Khi một Cộng Hưởng Giả trong đội tấn công mục tiêu trong &lt;color=#f4d582&gt;Bể Sét&lt;/color&gt;, Lưỡi Điện sẽ thực hiện Tấn Công Phối Hợp, gây &lt;color=#9656d8ff&gt;Sát Thương Electro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -16164,7 +16164,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Yuanwu: Hướng dẫn Resonance Skill &lt;color=#f4d582&gt;Thunder Field&lt;/color&gt;</t>
+          <t>Yuanwu: Hướng dẫn Kỹ năng Cộng Hưởng &lt;color=#f4d582&gt;Trường Sấm Sét&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -16229,7 +16229,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -16294,7 +16294,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Khi "Sẵn Sàng" đầy, giữ Leihuang Master để tiêu hao toàn bộ "Sẵn Sàng" và tung Rumbling Spark, gây &lt;color=#9656d8ff&gt;Electro DMG&lt;/color&gt; và bước vào trạng thái &lt;color=#d4bf5f&gt;Lightning Infused&lt;/color&gt;.</t>
+          <t>Khi "Sẵn Sàng" đầy, giữ Leihuang Master để tiêu hao toàn bộ "Sẵn Sàng" và tung Rumbling Spark, gây &lt;color=#9656d8ff&gt;Sát Thương Electro&lt;/color&gt; và bước vào trạng thái &lt;color=#d4bf5f&gt;Thấm Điện&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -16359,7 +16359,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Yuanwu: Hướng dẫn Resonance Skill &lt;color=#d4bf5f&gt;Rumbling Spark&lt;/color&gt;</t>
+          <t>Yuanwu: Hướng dẫn Kỹ năng Cộng Hưởng &lt;color=#d4bf5f&gt;Tia Lửa Gầm Ù&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Trong trạng thái &lt;color=#d4bf5f&gt;Lightning Infused&lt;/color&gt;: &lt;color=Highlight&gt;Basic Attack&lt;/color&gt;, &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; và &lt;color=Highlight&gt;Dodge Counter&lt;/color&gt; đều được tăng cường; khả năng chống gián đoạn tăng lên; hiệu suất deplete Vibration Strength Đối Phương cũng được cải thiện.</t>
+          <t>Trong trạng thái &lt;color=#d4bf5f&gt;Thấm Điện&lt;/color&gt;: &lt;color=Highlight&gt;Đòn Cơ Bản&lt;/color&gt;, &lt;color=Highlight&gt;Đòn Nặng&lt;/color&gt; và &lt;color=Highlight&gt;Dodge Counter Tránh&lt;/color&gt; đều được tăng cường; khả năng chống gián đoạn tăng lên; hiệu suất tiêu hao Sức Rung Đối Phương cũng được cải thiện.</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Yuanwu: Hướng dẫn Resonance Skill &lt;color=#d4bf5f&gt;Lightning Infused&lt;/color&gt;</t>
+          <t>Yuanwu: Hướng dẫn Kỹ năng Cộng Hưởng &lt;color=#d4bf5f&gt;Thiên Lôi Thấm Nhuần&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -16619,7 +16619,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -16684,7 +16684,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Đánh thức sức mạnh sấm sét, ban &lt;color=#d4bf5f&gt;Lightning Infused&lt;/color&gt; cho tất cả Resonator trong đội gần đó, rồi tấn công mục tiêu với toàn lực, gây &lt;color=#9656d8ff&gt;Electro DMG&lt;/color&gt;.</t>
+          <t>Đánh thức sức mạnh sấm sét, ban &lt;color=#d4bf5f&gt;Hiệu ứng Sét Nhiễm&lt;/color&gt; cho tất cả Cộng Hưởng Giả trong đội gần đó, rồi tấn công mục tiêu với toàn lực, gây &lt;color=#9656d8ff&gt;Sát Thương Electro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -16749,7 +16749,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Yuanwu: Hướng dẫn Resonance Liberation</t>
+          <t>Yuanwu: Resonance Liberation Tutorial</t>
         </is>
       </c>
     </row>
@@ -16879,7 +16879,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;. Khi Đòn Attack 4 trúng mục tiêu, nhận được 1 Giai Điệu.</t>
+          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;. Khi Đòn Tấn Công 4 trúng mục tiêu, nhận được 1 Giai Điệu.</t>
         </is>
       </c>
     </row>
@@ -16944,7 +16944,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Yangyang: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Yangyang: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -17009,7 +17009,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Chém đứt trường gió bằng lưỡi kiếm, kéo các mục tiêu xung quanh vào trung tâm trường gió, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; và nhận 1 Giai Điệu.</t>
+          <t>Chém đứt trường gió bằng lưỡi kiếm, kéo các mục tiêu xung quanh vào trung tâm trường gió, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; và nhận 1 Giai Điệu.</t>
         </is>
       </c>
     </row>
@@ -17074,7 +17074,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Yangyang: Hướng dẫn Resonance Skill</t>
+          <t>Yangyang: Resonance Skill Tutorial</t>
         </is>
       </c>
     </row>
@@ -17139,7 +17139,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -17204,7 +17204,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Tiêu hao STA và lao về phía trước, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;. Thực hiện Basic Attack ngay sau Heavy Attack để phóng lưỡi gió, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; và nhận 1 Giai Điệu.</t>
+          <t>Tiêu hao STA và lao về phía trước, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;. Thực hiện Đòn Cơ Bản ngay sau Đòn Nặng để phóng lưỡi gió, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; và nhận 1 Giai Điệu.</t>
         </is>
       </c>
     </row>
@@ -17269,7 +17269,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Yangyang: &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt;</t>
+          <t>Yangyang: &lt;color=#d4bf5f&gt;Hướng dẫn Tấn Công Mạnh&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -17334,7 +17334,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Khi có 3 Giai Điệu, Kỹ Năng Bão Tố có thể được kích hoạt sau khi Heavy Attack trúng mục tiêu, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.</t>
+          <t>Khi có 3 Giai Điệu, Kỹ Năng Bão Tố có thể được kích hoạt sau khi Đòn Tấn Công Mạnh trúng mục tiêu, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17399,7 +17399,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Yangyang: Hướng dẫn Forte Circuit &lt;color=#d4bf5f&gt;Stormy Strike&lt;/color&gt;</t>
+          <t>Yangyang: Hướng dẫn Forte Circuit &lt;color=#d4bf5f&gt;Đòn Đánh Bão Táp&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -17464,7 +17464,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Khi đang ở trên không và có 3 Giai Điệu, sử dụng &lt;color=#f4d582&gt;Mid-air Attack&lt;/color&gt; để tiêu hao toàn bộ Giai Điệu và tấn công, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;. Sau khi tiếp đất, tiếp tục tấn công bằng kiếm trong vỏ, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.</t>
+          <t>Khi đang ở trên không và có 3 Giai Điệu, sử dụng &lt;color=#f4d582&gt;Đòn Mid-air Attack&lt;/color&gt; để tiêu hao toàn bộ Giai Điệu và tấn công, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;. Sau khi tiếp đất, tiếp tục tấn công bằng kiếm trong vỏ, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17529,7 +17529,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Yangyang: Hướng dẫn Forte Circuit &lt;color=#d4bf5f&gt;Mid-air Attack: Feather Release&lt;/color&gt;</t>
+          <t>Yangyang: Hướng dẫn Forte Circuit &lt;color=#d4bf5f&gt;Tấn Công Giữa Không: Giải Phóng Lông Vũ&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -17594,7 +17594,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Vung kiếm tạo ra lốc xoáy, hút các mục tiêu xung quanh vào trung tâm, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.</t>
+          <t>Vung kiếm tạo ra lốc xoáy, hút các mục tiêu xung quanh vào trung tâm, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17659,7 +17659,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Yangyang: Hướng dẫn Resonance Liberation</t>
+          <t>Yangyang: Resonance Liberation Tutorial</t>
         </is>
       </c>
     </row>
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Basic Attack của Yangyang gồm 4 giai đoạn, giai đoạn cuối sẽ nhận được 1 Thanh Forte.</t>
+          <t>Đòn Basic Attack của Yangyang gồm 4 giai đoạn, giai đoạn cuối sẽ nhận được 1 Thanh Forte.</t>
         </is>
       </c>
     </row>
@@ -17984,7 +17984,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Khi Thanh Forte chưa đầy, giữ Basic Attack để kích hoạt Heavy Attack xuyên phá kẻ địch, sau đó dùng Basic Attack để thực hiện đòn tấn công tiếp nối.</t>
+          <t>Khi Thanh Forte chưa đầy, giữ Basic Attack để kích hoạt Đòn Tấn Công Mạnh xuyên phá kẻ địch, sau đó dùng Basic Attack để thực hiện đòn tấn công tiếp nối.</t>
         </is>
       </c>
     </row>
@@ -18049,7 +18049,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Heavy Attack: Thanh Forte chưa đầy</t>
+          <t>Đòn Heavy Attack: Thanh Forte chưa đầy</t>
         </is>
       </c>
     </row>
@@ -18114,7 +18114,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Khi Thanh Forte đầy, Heavy Attack sẽ tự động kích hoạt một cú uppercut khi trúng mục tiêu. Thực hiện Basic Attack trên không để kích hoạt đòn lao xuống mạnh mẽ.</t>
+          <t>Khi Thanh Forte đầy, Đòn Tấn Công Mạnh sẽ tự động kích hoạt một cú uppercut khi trúng mục tiêu. Thực hiện Đòn Basic Attack trên không để kích hoạt đòn lao xuống mạnh mẽ.</t>
         </is>
       </c>
     </row>
@@ -18179,7 +18179,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Heavy Attack: Thanh Forte đã đầy</t>
+          <t>Đòn Heavy Attack: Thanh Forte đã đầy</t>
         </is>
       </c>
     </row>
@@ -18244,7 +18244,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Khi Thanh Forte đầy, Heavy Attack sẽ tự động kích hoạt một cú uppercut khi trúng mục tiêu. Thực hiện Basic Attack trên không để kích hoạt đòn lao xuống mạnh mẽ.</t>
+          <t>Khi Thanh Forte đầy, Đòn Tấn Công Mạnh sẽ tự động kích hoạt một cú uppercut khi trúng mục tiêu. Thực hiện Đòn Basic Attack trên không để kích hoạt đòn lao xuống mạnh mẽ.</t>
         </is>
       </c>
     </row>
@@ -18309,7 +18309,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Heavy Attack: Thanh Forte đã đầy</t>
+          <t>Đòn Heavy Attack: Thanh Forte đã đầy</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -18439,7 +18439,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Khi Thanh Forte đầy, Heavy Attack sẽ tự động kích hoạt một cú uppercut khi trúng mục tiêu. Thực hiện Basic Attack trên không để kích hoạt đòn lao xuống mạnh mẽ.</t>
+          <t>Khi Thanh Forte đầy, Đòn Tấn Công Mạnh sẽ tự động kích hoạt một cú uppercut khi trúng mục tiêu. Thực hiện Đòn Basic Attack trên không để kích hoạt đòn lao xuống mạnh mẽ.</t>
         </is>
       </c>
     </row>
@@ -18504,7 +18504,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Heavy Attack: Giai Điệu Hoàn Chỉnh</t>
+          <t>Đòn Heavy Attack: Giai Điệu Hoàn Chỉnh</t>
         </is>
       </c>
     </row>
@@ -18569,7 +18569,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Khi Thanh Forte đầy, dùng Basic Attack trên không để kích hoạt Đòn Lao Xuống Nâng Cao.</t>
+          <t>Khi Thanh Forte đầy, dùng Đòn Basic Attack trên không để kích hoạt Đòn Lao Xuống Nâng Cao.</t>
         </is>
       </c>
     </row>
@@ -18699,7 +18699,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Đòn Lao Xuống Giữa Không: Thanh Forte đầy</t>
+          <t>Tấn Công Lao Xuống Giữa Không: Thanh Forte đầy</t>
         </is>
       </c>
     </row>
@@ -18764,7 +18764,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Bắn tối đa 5 phát liên tiếp, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;, Basic Attack 4 sẽ bắn sương mù về phía trước.</t>
+          <t>Bắn tối đa 5 phát liên tiếp, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;, Đòn Basic Attack 4 sẽ bắn sương mù về phía trước.</t>
         </is>
       </c>
     </row>
@@ -18829,7 +18829,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Aalto: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Aalto: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -18894,7 +18894,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Tạo ra Mist và 1 Avatar Mist để khiêu khích các mục tiêu xung quanh. Avatar sẽ kế thừa một phần HP của Aalto và tạo ra 6 &lt;color=#f4d582&gt;Mist Bullets&lt;/color&gt; xung quanh, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; khi trúng đích.</t>
+          <t>Tạo ra Sương mù và 1 Hóa Thân Sương mù để khiêu khích các mục tiêu xung quanh. Hóa Thân sẽ kế thừa một phần HP của Aalto và tạo ra 6 &lt;color=#f4d582&gt;Đạn Sương mù&lt;/color&gt; xung quanh, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; khi trúng đích.</t>
         </is>
       </c>
     </row>
@@ -18959,7 +18959,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Aalto: Hướng dẫn Resonance Skill &lt;color=#d4bf5f&gt;Mist Avatar&lt;/color&gt;</t>
+          <t>Aalto: Hướng dẫn Resonance Skill &lt;color=#d4bf5f&gt;Hóa Thân Sương Mù&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -19024,7 +19024,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -19089,7 +19089,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Bắt đầu ngắm để tung đòn tấn công gây sát thương cao hơn. Sau khi nạp đủ, thực hiện cú bắn mạnh, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.</t>
+          <t>Bắt đầu ngắm để tung đòn tấn công gây DMG cao hơn. Sau khi nạp đủ, thực hiện cú bắn mạnh, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -19154,7 +19154,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Aalto: &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt;</t>
+          <t>Aalto: &lt;color=#d4bf5f&gt;Hướng dẫn Tấn Công Mạnh&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -19219,7 +19219,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Bắt đầu ngắm để tung đòn tấn công gây sát thương cao hơn. Sau khi nạp đủ, thực hiện cú bắn mạnh, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.</t>
+          <t>Bắt đầu ngắm để tung đòn tấn công gây DMG cao hơn. Sau khi nạp đủ, thực hiện cú bắn mạnh, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -19284,7 +19284,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Aalto: &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt;</t>
+          <t>Aalto: &lt;color=#d4bf5f&gt;Hướng dẫn Tấn Công Mạnh&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -19349,7 +19349,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Đòn &lt;color=#f4d582&gt;Basic Attack&lt;/color&gt; và &lt;color=#f4d582&gt;Mid-Air Attack&lt;/color&gt; gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; và hồi phục giọt Sương nếu xuyên qua Sương.</t>
+          <t>Đòn &lt;color=#f4d582&gt;Basic Attack&lt;/color&gt; và &lt;color=#f4d582&gt;Tấn Công Giữa Không&lt;/color&gt; gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; và hồi phục giọt Sương nếu xuyên qua Sương.</t>
         </is>
       </c>
     </row>
@@ -19414,7 +19414,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Aalto: Hướng dẫn Forte Circuit &lt;color=#d4bf5f&gt;Mist Salvo&lt;/color&gt;</t>
+          <t>Aalto: Hướng dẫn Forte Circuit &lt;color=#d4bf5f&gt;Loạt Súng Sương Mù&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -19479,7 +19479,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Đi qua Sương Mù hoặc Cổng Lưỡng Nan để bước vào &lt;color=#f4d582&gt;Mistcloak Dash&lt;/color&gt;, tăng Movement Speed. Trong trạng thái &lt;color=#f4d582&gt;Mistcloak Dash&lt;/color&gt;, liên tục tiêu hao Giọt Sương để tạo ra 1 &lt;color=#f4d582&gt;Mist Bullet&lt;/color&gt; cho mỗi Giọt Sương đã dùng, tự động tấn công mục tiêu và gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.</t>
+          <t>Đi qua Sương Mù hoặc Cổng Lưỡng Nan để bước vào &lt;color=#f4d582&gt;Ẩn Thân Trong Sương&lt;/color&gt;, tăng Tốc Độ Di Chuyển. Trong trạng thái &lt;color=#f4d582&gt;Ẩn Thân Trong Sương&lt;/color&gt;, liên tục tiêu hao Giọt Sương để tạo ra 1 &lt;color=#f4d582&gt;Đạn Sương&lt;/color&gt; cho mỗi Giọt Sương đã dùng, tự động tấn công mục tiêu và gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -19609,7 +19609,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Aalto: Hướng dẫn Forte Circuit &lt;color=#d4bf5f&gt;Mist Cover&lt;/color&gt;</t>
+          <t>Aalto: Hướng dẫn Forte Circuit &lt;color=#d4bf5f&gt;Màn Sương Che Phủ&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -19674,7 +19674,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -19739,7 +19739,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Tiêu hao STA và bắn liên tiếp vào mục tiêu trên không, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA và bắn liên tiếp vào mục tiêu trên không, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -19804,7 +19804,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Tạo ra "Cánh Gate of Quandary" trong 10 giây. Đạn đi qua "Cánh Gate of Quandary" sẽ gây sát thương tăng cường.</t>
+          <t>Tạo ra "Cánh Cổng Băn Khoăn" trong 10 giây. Đạn đi qua "Cánh Cổng Băn Khoăn" sẽ gây sát thương tăng cường.</t>
         </is>
       </c>
     </row>
@@ -19869,7 +19869,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Aalto: Hướng dẫn Resonance Liberation</t>
+          <t>Aalto: Resonance Liberation Tutorial</t>
         </is>
       </c>
     </row>
@@ -19934,7 +19934,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 5 đòn tấn công liên tiếp, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.</t>
+          <t>Thực hiện tối đa 5 đòn tấn công liên tiếp, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -19999,7 +19999,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Jiyan: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Jiyan: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -20064,7 +20064,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Lao về phía trước, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; lên mục tiêu trên đường đi. Có thể sử dụng khi đang bay.</t>
+          <t>Lao về phía trước, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; lên mục tiêu trên đường đi. Có thể sử dụng khi đang bay.</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -20259,7 +20259,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Sau khi dùng &lt;color=#f4d582&gt;Windqueller&lt;/color&gt; trên không, Basic Attack để thực hiện đòn đánh trên không, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.</t>
+          <t>Sau khi dùng &lt;color=#f4d582&gt;Windqueller&lt;/color&gt; trên không, Basic Attack để thực hiện đòn đánh trên không, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -20389,7 +20389,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Thả nút Normal Attack trong &lt;color=#f4d582&gt;Heavy Attack&lt;/color&gt; để tung ra Vết Rạch Abyssal sau khi Heavy Attack kết thúc, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.</t>
+          <t>Thả nút Normal Attack trong &lt;color=#f4d582&gt;Đòn Tấn Công Mạnh&lt;/color&gt; để tung ra Vết Rạch Vực Sâu sau khi Đòn Tấn Công Mạnh kết thúc, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -20584,7 +20584,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Thả trong Heavy Attack</t>
+          <t>Thả trong Đòn Tấn Công Mạnh</t>
         </is>
       </c>
     </row>
@@ -20649,7 +20649,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Giữ Basic Attack trong khi thi triển &lt;color=#f4d582&gt;Heavy Attack&lt;/color&gt; để tung đòn Hất Gió sau khi Heavy Attack kết thúc, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;. Sử dụng Basic Attack sau &lt;color=#f4d582&gt;Heavy Attack: Windborne Strike&lt;/color&gt; để thực hiện các đòn tấn công trên không, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.</t>
+          <t>Giữ Đòn Basic Attack trong khi thi triển &lt;color=#f4d582&gt;Đòn Tấn Công Mạnh&lt;/color&gt; để tung đòn Hất Gió sau khi Đòn Tấn Công Mạnh kết thúc, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;. Sử dụng Đòn Basic Attack sau &lt;color=#f4d582&gt;Đòn Tấn Công Mạnh: Hất Gió&lt;/color&gt; để thực hiện các đòn tấn công trên không, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -20779,7 +20779,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Tiêu hao STA và phóng lao từ trên không đâm xuống đất, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;. Sau khi lao cắm xuống đất, dùng &lt;color=#f4d582&gt;Basic Attack&lt;/color&gt; để thực hiện thêm 1 đòn tấn công, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA và phóng lao từ trên không đâm xuống đất, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;. Sau khi lao cắm xuống đất, dùng &lt;color=#f4d582&gt;Đòn Cơ Bản&lt;/color&gt; để thực hiện thêm 1 đòn tấn công, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -20844,7 +20844,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Kích hoạt &lt;color=#f4d582&gt;Qingloong Mode&lt;/color&gt; sau khi thi triển Bão Ngọc: Khúc Dạo Đầu. Trong &lt;color=#f4d582&gt;Qingloong Mode&lt;/color&gt;, &lt;color=#f4d582&gt;Basic Attack&lt;/color&gt; và &lt;color=#f4d582&gt;Heavy Attack&lt;/color&gt; sẽ được thay thế bằng Ngọn Giáo Qingloong, thực hiện tối đa 3 đòn tấn công liên tiếp, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;, được tính là Sát Thương Heavy Attack.</t>
+          <t>Kích hoạt &lt;color=#f4d582&gt;Chế Độ Thanh Long&lt;/color&gt; sau khi thi triển Bão Ngọc: Khúc Dạo Đầu. Trong &lt;color=#f4d582&gt;Chế Độ Thanh Long&lt;/color&gt;, &lt;color=#f4d582&gt;Đòn Cơ Bản&lt;/color&gt; và &lt;color=#f4d582&gt;Đòn Nặng&lt;/color&gt; sẽ được thay thế bằng Ngọn Giáo Thanh Long, thực hiện tối đa 3 đòn tấn công liên tiếp, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;, được tính là Sát Thương Đòn Nặng.</t>
         </is>
       </c>
     </row>
@@ -20909,7 +20909,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Jiyan: Hướng dẫn Resonance Liberation</t>
+          <t>Jiyan: Resonance Liberation Tutorial</t>
         </is>
       </c>
     </row>
@@ -20974,7 +20974,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Nếu Điểm Quyết Tâm trên 30 khi kích hoạt &lt;color=#f4d582&gt;Resonance Liberation: Emerald Storm: Prelude&lt;/color&gt;, tiêu hao 30 Điểm Quyết Tâm để thay thế bằng Bão Ngọc Lục - Khúc Kết, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;, được tính là Sát Thương Heavy Attack. Có thể kích hoạt khi đang bay.</t>
+          <t>Nếu Điểm Quyết Tâm trên 30 khi kích hoạt &lt;color=#f4d582&gt;Resonance Liberation: Bão Ngọc Lục - Khúc Dạo Đầu&lt;/color&gt;, tiêu hao 30 Điểm Quyết Tâm để thay thế bằng Bão Ngọc Lục - Khúc Kết, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;, được tính là Sát Thương Đòn Nặng. Có thể kích hoạt khi đang bay.</t>
         </is>
       </c>
     </row>
@@ -21104,7 +21104,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 4 đòn tấn công bằng võ thuật mạnh mẽ, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;. &lt;color=#f4d582&gt;Normal Attacks&lt;/color&gt; sẽ tích Chi khi trúng mục tiêu.</t>
+          <t>Thực hiện tối đa 4 đòn tấn công bằng võ thuật mạnh mẽ, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;. &lt;color=#f4d582&gt;Đòn Normal Attack&lt;/color&gt; sẽ tích Chi khi trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -21169,7 +21169,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Jianxin: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Jianxin: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -21234,7 +21234,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để tung cú đá lao xuống, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để tung cú đá lao xuống, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -21299,7 +21299,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để tấn công mục tiêu, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;. Gây trúng mục tiêu sẽ nhận được "Khí".</t>
+          <t>Tiêu hao STA để tấn công mục tiêu, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;. Gây trúng mục tiêu sẽ nhận được "Khí".</t>
         </is>
       </c>
     </row>
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Jianxin: &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt;</t>
+          <t>Jianxin: &lt;color=#d4bf5f&gt;Hướng dẫn Tấn Công Mạnh&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -21429,7 +21429,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Jianxin: &lt;color=#d4bf5f&gt;Resonance Skill&lt;/color&gt;</t>
+          <t>Jianxin: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Skill&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -21495,8 +21495,8 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Khi "Khí" tích đủ tối đa, nhấn giữ &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; để bắt đầu nạp. Gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; lên khu vực gần đó và dần tiêu hao "Khí". Mỗi giai đoạn tiến triển sẽ nhận được lá chắn tạm thời và gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;, tiến tới tối đa &lt;color=Highlight&gt;Major Zhoutian: Outer&lt;/color&gt;. Nhả &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; để ngắt nạp và tung đòn tấn công tương ứng với giai đoạn hiện tại.
-&lt;color=Highlight&gt;Prior to Minor Zhoutian&lt;/color&gt;: Nhận lá chắn cấp 1 và tung &lt;color=Highlight&gt;Pushing Punch&lt;/color&gt;, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; lên kẻ địch phía trước khi bị ngắt nạp.</t>
+          <t>Khi "Khí" tích đủ tối đa, nhấn giữ &lt;color=Highlight&gt;Đòn Heavy Attack&lt;/color&gt; để bắt đầu nạp. Gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; lên khu vực gần đó và dần tiêu hao "Khí". Mỗi giai đoạn tiến triển sẽ nhận được lá chắn tạm thời và gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;, tiến tới tối đa &lt;color=Highlight&gt;Chu Thiên Đại: Ngoại&lt;/color&gt;. Nhả &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt; để ngắt nạp và tung đòn tấn công tương ứng với giai đoạn hiện tại.
+&lt;color=Highlight&gt;Trước Chu Thiên Tiểu&lt;/color&gt;: Nhận lá chắn cấp 1 và tung &lt;color=Highlight&gt;Đấm Đẩy&lt;/color&gt;, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; lên kẻ địch phía trước khi bị ngắt nạp.</t>
         </is>
       </c>
     </row>
@@ -21561,7 +21561,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Jianxin: &lt;color=#d4bf5f&gt;Resonance Circuit&lt;/color&gt;</t>
+          <t>Jianxin: &lt;color=#d4bf5f&gt;Hướng dẫn Mạch Cộng Hưởng&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -21626,7 +21626,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Major Zhoutian: Outer&lt;/color&gt;: Nhận lá chắn cấp 4 và phóng &lt;color=Highlight&gt;Shock&lt;/color&gt; để gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; lên các mục tiêu xung quanh.</t>
+          <t>&lt;color=Highlight&gt;Chu Thiên Chính: Ngoại&lt;/color&gt;: Nhận lá chắn cấp 4 và phóng &lt;color=Highlight&gt;Shock&lt;/color&gt; để gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; lên các mục tiêu xung quanh.</t>
         </is>
       </c>
     </row>
@@ -21691,7 +21691,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Jianxin: &lt;color=#d4bf5f&gt;Resonance Circuit&lt;/color&gt;</t>
+          <t>Jianxin: &lt;color=#d4bf5f&gt;Hướng dẫn Mạch Cộng Hưởng&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -21756,7 +21756,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Tạo một vùng gió mạnh, liên tục kéo các mục tiêu trong vùng về trung tâm và gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;. Khi vùng gió tan biến, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; một lần nữa lên tất cả mục tiêu trong phạm vi.</t>
+          <t>Tạo một vùng gió mạnh, liên tục kéo các mục tiêu trong vùng về trung tâm và gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;. Khi vùng gió tan biến, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; một lần nữa lên tất cả mục tiêu trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -21821,7 +21821,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Jianxin: &lt;color=#d4bf5f&gt;Resonance Liberation&lt;/color&gt;</t>
+          <t>Jianxin: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Liberation&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -21886,7 +21886,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Tạo thành chuỗi tối đa 3 đòn tấn công liên tiếp, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.</t>
+          <t>Tạo thành chuỗi tối đa 3 đòn tấn công liên tiếp, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -21951,7 +21951,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Qiuyuan: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Qiuyuan: &lt;color=#d4bf5f&gt;Hướng Dẫn Basic Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -22016,7 +22016,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Khi Độ Trữ Tâm Kiếm đạt 200 điểm, &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; được thay thế bằng &lt;color=Highlight&gt;Thus Spoke the Blade: Inkwash&lt;/color&gt;, thực hiện tối đa 4 đòn liên tiếp, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;, được tính là Sát Thương Heavy Attack.</t>
+          <t>Khi Độ Trữ Tâm Kiếm đạt 200 điểm, &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt; được thay thế bằng &lt;color=Highlight&gt;Lời Kiếm Phán: Mực Loang&lt;/color&gt;, thực hiện tối đa 4 đòn liên tiếp, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;, được tính là Sát Thương Đòn Tấn Công Mạnh.</t>
         </is>
       </c>
     </row>
@@ -22081,7 +22081,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để tấn công mục tiêu, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;. {Cus:Ipt,Touch=Touch PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau đó để thi triển &lt;color=Highlight&gt;Thus Spoke the Blade: Inkwash&lt;/color&gt; Cấp 4.</t>
+          <t>Tiêu hao STA để tấn công mục tiêu, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Đòn Normal Attack&lt;/color&gt; ngay sau đó để thi triển &lt;color=Highlight&gt;Lưỡi Kiếm Lên Tiếng: Mực Tàu&lt;/color&gt; Cấp 4.</t>
         </is>
       </c>
     </row>
@@ -22146,7 +22146,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Qiuyuan: &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt;</t>
+          <t>Qiuyuan: &lt;color=#d4bf5f&gt;Hướng Dẫn Tấn Công Mạnh&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -22211,7 +22211,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để tấn công mục tiêu, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;. {Cus:Ipt,Touch=Touch PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau đó để thi triển &lt;color=Highlight&gt;Thus Spoke the Blade: Inkwash&lt;/color&gt; Cấp 4.</t>
+          <t>Tiêu hao STA để tấn công mục tiêu, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Đòn Normal Attack&lt;/color&gt; ngay sau đó để thi triển &lt;color=Highlight&gt;Lưỡi Kiếm Lên Tiếng: Mực Tàu&lt;/color&gt; Cấp 4.</t>
         </is>
       </c>
     </row>
@@ -22276,7 +22276,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Qiuyuan: &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt;</t>
+          <t>Qiuyuan: &lt;color=#d4bf5f&gt;Hướng Dẫn Chuỗi Tấn Công Mạnh&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -22344,9 +22344,9 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Khi Độ Trữ Tâm Kiếm đạt tối đa, Qiuyuan bước vào trạng thái &lt;color=Highlight&gt;Inksplash of Mind&lt;/color&gt;, trong đó &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; được thay thế bằng Heavy Attack &lt;color=Highlight&gt;Thus Spoke the Blade: To Save&lt;/color&gt; trong 8 giây.
-Trong trạng thái Mực Tâm Loang, giữ &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; để tiêu hao Độ Trữ Tâm Kiếm và thực hiện Heavy Attack &lt;color=Highlight&gt;Thus Spoke the Blade: To Teach&lt;/color&gt;, &lt;color=Highlight&gt;Thus Spoke the Blade: To Save&lt;/color&gt; và &lt;color=Highlight&gt;Thus Spoke the Blade: To Sacrifice&lt;/color&gt; liên tiếp, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;, được tính là Sát Thương Heavy Attack.
-- Thực hiện &lt;color=Highlight&gt;Thus Spoke the Blade: To Teach&lt;/color&gt;, &lt;color=Highlight&gt;Thus Spoke the Blade: To Save&lt;/color&gt; hoặc &lt;color=Highlight&gt;Thus Spoke the Blade: To Sacrifice&lt;/color&gt; được tính là sử dụng &lt;color=Highlight&gt;Echo Skill&lt;/color&gt;.
+          <t>Khi Độ Trữ Tâm Kiếm đạt tối đa, Qiuyuan bước vào trạng thái &lt;color=Highlight&gt;Mực Tâm Loang&lt;/color&gt;, trong đó &lt;color=Highlight&gt;Đòn Tấn Công Mạnh&lt;/color&gt; được thay thế bằng Đòn Tấn Công Mạnh &lt;color=Highlight&gt;Lời Kiếm Phán: Cứu Độ&lt;/color&gt; trong 8 giây.
+Trong trạng thái Mực Tâm Loang, giữ &lt;color=Highlight&gt;Đòn Normal Attack&lt;/color&gt; để tiêu hao Độ Trữ Tâm Kiếm và thực hiện Đòn Tấn Công Mạnh &lt;color=Highlight&gt;Lời Kiếm Phán: Dạy Dỗ&lt;/color&gt;, &lt;color=Highlight&gt;Lời Kiếm Phán: Cứu Độ&lt;/color&gt; và &lt;color=Highlight&gt;Lời Kiếm Phán: Hy Sinh&lt;/color&gt; liên tiếp, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;, được tính là Sát Thương Đòn Tấn Công Mạnh.
+- Thực hiện &lt;color=Highlight&gt;Lời Kiếm Phán: Dạy Dỗ&lt;/color&gt;, &lt;color=Highlight&gt;Lời Kiếm Phán: Cứu Độ&lt;/color&gt; hoặc &lt;color=Highlight&gt;Lời Kiếm Phán: Hy Sinh&lt;/color&gt; được tính là sử dụng &lt;color=Highlight&gt;Kỹ Năng Echo&lt;/color&gt;.
 - Trạng thái Mực Tâm Loang kết thúc khi Độ Trữ Tâm Kiếm cạn kiệt.</t>
         </is>
       </c>
@@ -22412,7 +22412,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để thực hiện Đòn Lao Xuống, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để thực hiện Đòn Lao Xuống, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -22478,8 +22478,8 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để lao về phía trước một đoạn, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;, được tính là Sát Thương Kỹ Năng Vọng Âm. Nếu &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; được thi triển khi bị tấn công bởi mục tiêu địch, Qiuyuan sẽ miễn nhiễm với sát thương trong lần này và làm chậm kẻ địch xung quanh, đồng thời không bị gián đoạn trong quá trình thi triển &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt;.
-Chuyển sang Resonators khác sẽ loại bỏ hiệu ứng làm chậm khỏi kẻ địch.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để lao về phía trước một đoạn, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;, được tính là Sát Thương Kỹ Năng Vọng Âm. Nếu &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; được thi triển khi bị tấn công bởi mục tiêu địch, Qiuyuan sẽ miễn nhiễm với DMG trong lần này và làm chậm kẻ địch xung quanh, đồng thời không bị gián đoạn trong quá trình thi triển &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt;.
+Chuyển sang Resonator khác sẽ loại bỏ hiệu ứng làm chậm khỏi kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -22544,7 +22544,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Qiuyuan: &lt;color=#d4bf5f&gt;Resonance Skill&lt;/color&gt;</t>
+          <t>Qiuyuan: &lt;color=#d4bf5f&gt;Hướng dẫn Kỹ năng Cộng Hưởng&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -22610,8 +22610,8 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Giữ &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để lao về phía trước và gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;, được tính là Sát Thương Kỹ Năng Vang Âm.
-Nếu không có mục tiêu nào gần đó khi giữ &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt;, Qiuyuan sẽ bật lên và bay lướt trong không trung bằng cách liên tục tiêu hao STA cho đến khi cạn kiệt. Thả &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để kết thúc lao đi và hạ cánh ngay lập tức. Nếu có mục tiêu gần đó khi Qiuyuan hạ cánh, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; lên các mục tiêu xung quanh, được tính là Sát Thương Kỹ Năng Vang Âm. Skill này có thể sử dụng khi đang ở trên không.</t>
+          <t>Giữ &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để lao về phía trước và gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;, được tính là Sát Thương Kỹ Năng Vang Âm.
+Nếu không có mục tiêu nào gần đó khi giữ &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt;, Qiuyuan sẽ bật lên và bay lướt trong không trung bằng cách liên tục tiêu hao STA cho đến khi cạn kiệt. Thả &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để kết thúc lao đi và hạ cánh ngay lập tức. Nếu có mục tiêu gần đó khi Qiuyuan hạ cánh, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; lên các mục tiêu xung quanh, được tính là Sát Thương Kỹ Năng Vang Âm. Kỹ năng này có thể sử dụng khi đang ở trên không.</t>
         </is>
       </c>
     </row>
@@ -22677,8 +22677,8 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; lên các mục tiêu xung quanh, được tính là Sát Thương Kỹ Năng Echo.
-Với mỗi 1% Crit. Rate vượt quá 50% của Qiuyuan, việc sử dụng kỹ năng này sẽ tăng 2% Crit. DMG cho Resonators đang hoạt động trong đội ở gần trong 30 giây, tối đa 30%.</t>
+          <t>Gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; lên các mục tiêu xung quanh, được tính là Sát Thương Kỹ Năng Echo.
+Với mỗi 1% Crit. Rate vượt quá 50% của Qiuyuan, việc sử dụng kỹ năng này sẽ tăng 2% Crit. DMG cho các Resonator đang hoạt động trong đội ở gần trong 30 giây, tối đa 30%.</t>
         </is>
       </c>
     </row>
@@ -22743,7 +22743,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Qiuyuan: &lt;color=#d4bf5f&gt;Resonance Liberation&lt;/color&gt;</t>
+          <t>Qiuyuan: &lt;color=#d4bf5f&gt;Hướng Dẫn Resonance Liberation&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -22808,7 +22808,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Thực hiện 4 đòn tấn công liên tiếp, gây &lt;color=#f9ff4a&gt;Spectro DMG&lt;/color&gt;. Nhận hiệu ứng "Âm Thanh Nhỏ Bé" khi trúng đích.</t>
+          <t>Thực hiện 4 đòn tấn công liên tiếp, gây &lt;color=#f9ff4a&gt;Sát Thương Spectro&lt;/color&gt;. Nhận hiệu ứng "Âm Thanh Nhỏ Bé" khi trúng đích.</t>
         </is>
       </c>
     </row>
@@ -22873,7 +22873,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Rover: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Rover: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -22938,7 +22938,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Từ trên không, phóng đòn tấn công lao xuống, gây &lt;color=#f9ff4a&gt;Spectro DMG&lt;/color&gt; và nhận "Âm Thanh Nhỏ Bé" khi trúng mục tiêu.</t>
+          <t>Từ trên không, phóng đòn tấn công lao xuống, gây &lt;color=#f9ff4a&gt;Sát Thương Spectro&lt;/color&gt; và nhận "Âm Thanh Nhỏ Bé" khi trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -23003,7 +23003,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Nhấn Basic Attack sau &lt;color=#f4d582&gt;Basic Attack 3&lt;/color&gt; hoặc &lt;color=#f4d582&gt;Heavy Attack&lt;/color&gt; vào thời điểm thích hợp để tung Kỹ Năng Nặng: Resonance, gây &lt;color=#f9ff4a&gt;Spectro DMG&lt;/color&gt;. Sau khi &lt;color=#f4d582&gt;Heavy Attack: Resonance&lt;/color&gt; trúng mục tiêu, nhấn Basic Attack để kích hoạt Kỹ Năng Nặng: Hậu Giai Điệu, gây &lt;color=#f9ff4a&gt;Spectro DMG&lt;/color&gt; và nhận hiệu ứng "Âm Thanh Nhỏ Bé" khi trúng đích.</t>
+          <t>Nhấn Basic Attack sau &lt;color=#f4d582&gt;Basic Attack 3&lt;/color&gt; hoặc &lt;color=#f4d582&gt;Kỹ Năng Nặng&lt;/color&gt; vào thời điểm thích hợp để tung Kỹ Năng Nặng: Cộng Hưởng, gây &lt;color=#f9ff4a&gt;Sát Thương Spectro&lt;/color&gt;. Sau khi &lt;color=#f4d582&gt;Kỹ Năng Nặng: Cộng Hưởng&lt;/color&gt; trúng mục tiêu, nhấn Basic Attack để kích hoạt Kỹ Năng Nặng: Hậu Giai Điệu, gây &lt;color=#f9ff4a&gt;Sát Thương Spectro&lt;/color&gt; và nhận hiệu ứng "Âm Thanh Nhỏ Bé" khi trúng đích.</t>
         </is>
       </c>
     </row>
@@ -23068,7 +23068,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Rover: Hướng dẫn Heavy Attack &lt;color=#d4bf5f&gt;Heavy Attack: Aftertune&lt;/color&gt;</t>
+          <t>Rover: Hướng dẫn Đòn Tấn Công Mạnh &lt;color=#d4bf5f&gt;Đòn Tấn Công Mạnh: Hậu Giai Điệu&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -23133,7 +23133,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Resonance</t>
+          <t>Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -23198,7 +23198,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Phóng một đòn tấn công về phía trước, gây &lt;color=#f9ff4a&gt;Spectro DMG&lt;/color&gt;.</t>
+          <t>Phóng một đòn tấn công về phía trước, gây &lt;color=#f9ff4a&gt;Sát Thương Spectro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -23328,7 +23328,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -23393,7 +23393,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Nếu "Âm Thanh Nhỏ" trên 50 khi sử dụng &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt;, tiêu hao 50 "Âm Thanh Nhỏ" để thay thế bằng &lt;color=Highlight&gt;Resonance Skill: Resonating Strikes&lt;/color&gt;, tung ra một đòn xoay tấn công về phía trước, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;. Sau khi &lt;color=Highlight&gt;Resonance Skill: Resonating Strikes&lt;/color&gt; kết thúc, nhấn Basic Attack để kích hoạt Basic Attack &lt;color=Highlight&gt;Resonating Echoes&lt;/color&gt;.</t>
+          <t>Nếu "Âm Thanh Nhỏ" trên 50 khi sử dụng &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt;, tiêu hao 50 "Âm Thanh Nhỏ" để thay thế bằng &lt;color=Highlight&gt;Resonance Skill: Đòn Công Kích Cộng Hưởng&lt;/color&gt;, tung ra một đòn xoay tấn công về phía trước, gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;. Sau khi &lt;color=Highlight&gt;Resonance Skill: Đòn Công Kích Cộng Hưởng&lt;/color&gt; kết thúc, nhấn Đòn Basic Attack để kích hoạt Đòn Basic Attack &lt;color=Highlight&gt;Echo Cộng Hưởng&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -23458,7 +23458,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Rover: Hướng dẫn Forte Circuit &lt;color=#d4bf5f&gt;Resonating Spin&lt;/color&gt;</t>
+          <t>Rover: Hướng dẫn Forte Circuit &lt;color=#d4bf5f&gt;Xoay Cộng Hưởng&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -23523,7 +23523,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -23588,7 +23588,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Tập trung năng lượng Spectro vào khu vực mục tiêu. Gây nổ sau một khoảng thời gian ngắn, gây &lt;color=#f9ff4a&gt;Spectro DMG&lt;/color&gt;.</t>
+          <t>Tập trung năng lượng Spectro vào khu vực mục tiêu. Gây nổ sau một khoảng thời gian ngắn, gây &lt;color=#f9ff4a&gt;Sát Thương Spectro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -23718,7 +23718,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Thực hiện 4 đòn tấn công liên tiếp, gây &lt;color=#f9ff4a&gt;Spectro DMG&lt;/color&gt;, và nhận hiệu ứng "Âm Thanh Nhỏ Bé" khi trúng đích.</t>
+          <t>Thực hiện 4 đòn tấn công liên tiếp, gây &lt;color=#f9ff4a&gt;Sát Thương Spectro&lt;/color&gt;, và nhận hiệu ứng "Âm Thanh Nhỏ Bé" khi trúng đích.</t>
         </is>
       </c>
     </row>
@@ -23783,7 +23783,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Rover - Hướng dẫn &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Vận Mệnh Giả - Hướng dẫn &lt;color=#d4bf5f&gt;Đòn Cơ Bản&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -23848,7 +23848,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Từ trên không, phóng đòn tấn công lao xuống, gây &lt;color=#f9ff4a&gt;Spectro DMG&lt;/color&gt; và nhận "Âm Thanh Nhỏ Bé" khi trúng mục tiêu.</t>
+          <t>Từ trên không, phóng đòn tấn công lao xuống, gây &lt;color=#f9ff4a&gt;Sát Thương Spectro&lt;/color&gt; và nhận "Âm Thanh Nhỏ Bé" khi trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -23913,7 +23913,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Nhấn Basic Attack sau &lt;color=#f4d582&gt;Basic Attack 3&lt;/color&gt; hoặc &lt;color=#f4d582&gt;Heavy Attack&lt;/color&gt; vào thời điểm thích hợp để tung Kỹ Năng Nặng: Resonance, gây &lt;color=#f9ff4a&gt;Spectro DMG&lt;/color&gt;. Sau khi &lt;color=#f4d582&gt;Heavy Attack: Resonance&lt;/color&gt; trúng mục tiêu, nhấn Basic Attack để kích hoạt Kỹ Năng Nặng: Hậu Giai Điệu, gây &lt;color=#f9ff4a&gt;Spectro DMG&lt;/color&gt; và nhận hiệu ứng "Âm Thanh Nhỏ Bé" khi trúng đích.</t>
+          <t>Nhấn Basic Attack sau &lt;color=#f4d582&gt;Basic Attack 3&lt;/color&gt; hoặc &lt;color=#f4d582&gt;Kỹ Năng Nặng&lt;/color&gt; vào thời điểm thích hợp để tung Kỹ Năng Nặng: Cộng Hưởng, gây &lt;color=#f9ff4a&gt;Sát Thương Spectro&lt;/color&gt;. Sau khi &lt;color=#f4d582&gt;Kỹ Năng Nặng: Cộng Hưởng&lt;/color&gt; trúng mục tiêu, nhấn Basic Attack để kích hoạt Kỹ Năng Nặng: Hậu Giai Điệu, gây &lt;color=#f9ff4a&gt;Sát Thương Spectro&lt;/color&gt; và nhận hiệu ứng "Âm Thanh Nhỏ Bé" khi trúng đích.</t>
         </is>
       </c>
     </row>
@@ -23978,7 +23978,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Rover: Hướng dẫn Heavy Attack &lt;color=#d4bf5f&gt;Heavy Attack: Aftertune&lt;/color&gt;</t>
+          <t>Rover: Hướng dẫn Đòn Tấn Công Mạnh &lt;color=#d4bf5f&gt;Đòn Tấn Công Mạnh: Hậu Giai Điệu&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -24043,7 +24043,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Resonance</t>
+          <t>Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -24108,7 +24108,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Phóng một đòn tấn công về phía trước, gây &lt;color=#f9ff4a&gt;Spectro DMG&lt;/color&gt;.</t>
+          <t>Phóng một đòn tấn công về phía trước, gây &lt;color=#f9ff4a&gt;Sát Thương Spectro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -24173,7 +24173,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Rover: Hướng dẫn Resonance Skill</t>
+          <t>Rover: Resonance Skill Tutorial</t>
         </is>
       </c>
     </row>
@@ -24238,7 +24238,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -24303,7 +24303,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Nếu "Âm Thanh Nhỏ" trên 50 khi sử dụng &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt;, tiêu hao 50 "Âm Thanh Nhỏ" để thay thế bằng &lt;color=Highlight&gt;Resonance Skill: Resonating Strikes&lt;/color&gt;, tung ra một đòn xoay tấn công về phía trước, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;. Sau khi &lt;color=Highlight&gt;Resonance Skill: Resonating Strikes&lt;/color&gt; kết thúc, nhấn Basic Attack để kích hoạt Basic Attack &lt;color=Highlight&gt;Resonating Echoes&lt;/color&gt;.</t>
+          <t>Nếu "Âm Thanh Nhỏ" trên 50 khi sử dụng &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt;, tiêu hao 50 "Âm Thanh Nhỏ" để thay thế bằng &lt;color=Highlight&gt;Resonance Skill: Đòn Công Kích Cộng Hưởng&lt;/color&gt;, tung ra một đòn xoay tấn công về phía trước, gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;. Sau khi &lt;color=Highlight&gt;Resonance Skill: Đòn Công Kích Cộng Hưởng&lt;/color&gt; kết thúc, nhấn Đòn Basic Attack để kích hoạt Đòn Basic Attack &lt;color=Highlight&gt;Echo Cộng Hưởng&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -24368,7 +24368,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Rover: Hướng dẫn Forte Circuit &lt;color=#d4bf5f&gt;Resonating Spin&lt;/color&gt;</t>
+          <t>Rover: Hướng dẫn Forte Circuit &lt;color=#d4bf5f&gt;Xoay Cộng Hưởng&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -24433,7 +24433,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -24498,7 +24498,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Tập trung năng lượng Spectro vào khu vực mục tiêu. Gây nổ sau một khoảng thời gian ngắn, gây &lt;color=#f9ff4a&gt;Spectro DMG&lt;/color&gt;.</t>
+          <t>Tập trung năng lượng Spectro vào khu vực mục tiêu. Gây nổ sau một khoảng thời gian ngắn, gây &lt;color=#f9ff4a&gt;Sát Thương Spectro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -24563,7 +24563,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Rover: Hướng dẫn Resonance Liberation</t>
+          <t>Rover: Resonance Liberation Tutorial</t>
         </is>
       </c>
     </row>
@@ -24628,7 +24628,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Nuôi dưỡng dây leo để thực hiện tối đa 5 đòn tấn công, gây &lt;color=#f9ff4a&gt;Spectro DMG&lt;/color&gt;. Khi trúng mục tiêu, nhận "Photosynthesis Energy" cho Basic Attack V.</t>
+          <t>Nuôi dưỡng dây leo để thực hiện tối đa 5 đòn tấn công, gây &lt;color=#f9ff4a&gt;Sát Thương Spectro&lt;/color&gt;. Khi trúng mục tiêu, nhận "Năng Lượng Quang Hợp" cho Đòn Basic Attack V.</t>
         </is>
       </c>
     </row>
@@ -24693,7 +24693,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Verina: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Verina: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -24758,7 +24758,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Tập trung năng lượng về phía trước, khiến thực vật mọc nhanh, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; diện rộng và nhận "Photosynthesis Energy".</t>
+          <t>Tập trung năng lượng về phía trước, khiến thực vật mọc nhanh, gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; diện rộng và nhận "Năng Lượng Quang Hợp".</t>
         </is>
       </c>
     </row>
@@ -24823,7 +24823,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Verina: Hướng dẫn Resonance Skill</t>
+          <t>Verina: Resonance Skill Tutorial</t>
         </is>
       </c>
     </row>
@@ -24888,7 +24888,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -24953,7 +24953,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để phóng về phía trước, gây &lt;color=#f9ff4a&gt;Spectro DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để phóng về phía trước, gây &lt;color=#f9ff4a&gt;Sát Thương Spectro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -25018,7 +25018,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Verina: &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt;</t>
+          <t>Verina: &lt;color=#d4bf5f&gt;Hướng dẫn Tấn Công Mạnh&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -25083,7 +25083,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Nhấn &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; sau khi dùng Kỹ Năng Nặng &lt;color=Highlight&gt;Starflower Blooms&lt;/color&gt; để thực hiện Mid-air Attack &lt;color=Highlight&gt;Starflower Blooms&lt;/color&gt;.</t>
+          <t>Nhấn &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; sau khi dùng Kỹ Năng Nặng &lt;color=Highlight&gt;Starflower Blooms&lt;/color&gt; để thực hiện Tấn Công Giữa Không &lt;color=Highlight&gt;Starflower Blooms&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -25148,7 +25148,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Khi sử dụng &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt;, có thể tiêu hao Photosynthesis Energy để hồi phục HP cho tất cả đồng đội xung quanh. &lt;color=Highlight&gt;Heavy Attack: Starflower Blooms&lt;/color&gt; gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.</t>
+          <t>Khi sử dụng &lt;color=Highlight&gt;Đòn Heavy Attack&lt;/color&gt;, có thể tiêu hao Năng Lượng Quang Hợp để hồi phục HP cho tất cả đồng đội xung quanh. &lt;color=Highlight&gt;Đòn Heavy Attack: Hoa Sao Nở Rộ&lt;/color&gt; gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -25213,7 +25213,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Verina: Hướng dẫn Forte Circuit &lt;color=#d4bf5f&gt;Heavy Attack: Starflower Blooms&lt;/color&gt;</t>
+          <t>Verina: Hướng dẫn Forte Circuit &lt;color=#d4bf5f&gt;Tấn Công Mạnh: Hoa Sao Nở Rộ&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -25278,7 +25278,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Thực hiện liên tiếp các đòn tấn công trên không, gây &lt;color=#f9ff4a&gt;Spectro DMG&lt;/color&gt;. &lt;color=Highlight&gt;Mid-air Attacks&lt;/color&gt; có thể tiêu hao "Photosynthesis Energy" để hồi phục Concerto Energy và HP cho tất cả Resonator trong đội gần đó.</t>
+          <t>Thực hiện liên tiếp các đòn tấn công trên không, gây &lt;color=#f9ff4a&gt;Sát Thương Spectro&lt;/color&gt;. &lt;color=Highlight&gt;Đòn Mid-air Attack&lt;/color&gt; có thể tiêu hao "Năng Lượng Quang Hợp" để hồi phục Concerto Energy và HP cho tất cả Cộng Hưởng Giả trong đội gần đó.</t>
         </is>
       </c>
     </row>
@@ -25343,7 +25343,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Thúc đẩy sự phát triển nhanh chóng của thực vật xung quanh, gây &lt;color=#f9ff4a&gt;Spectro DMG&lt;/color&gt;, phục hồi HP cho tất cả Resonator trong đội gần đó, và áp dụng &lt;color=#f4d582&gt;Photosynthesis Mark&lt;/color&gt; lên mục tiêu khi trúng đích.</t>
+          <t>Thúc đẩy sự phát triển nhanh chóng của thực vật xung quanh, gây &lt;color=#f9ff4a&gt;Sát Thương Spectro&lt;/color&gt;, phục hồi HP cho tất cả Cộng Hưởng Giả trong đội gần đó, và áp dụng &lt;color=#f4d582&gt;Dấu Hiệu Quang Hợp&lt;/color&gt; lên mục tiêu khi trúng đích.</t>
         </is>
       </c>
     </row>
@@ -25408,7 +25408,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Verina: Hướng dẫn Resonance Liberation</t>
+          <t>Verina: Resonance Liberation Tutorial</t>
         </is>
       </c>
     </row>
@@ -25473,7 +25473,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Khi bất kỳ Resonator gần đó trong đội tấn công mục tiêu có dấu Photosynthesis Mark, Verina sẽ phát động Attack Phối Hợp, gây &lt;color=#f9ff4a&gt;Spectro DMG&lt;/color&gt; và hồi máu cho nhân vật gây sát thương trong đội gần đó.</t>
+          <t>Khi bất kỳ Resonator gần đó trong đội tấn công mục tiêu có dấu Photosynthesis Mark, Verina sẽ phát động Tấn Công Phối Hợp, gây &lt;color=#f9ff4a&gt;Spectro DMG&lt;/color&gt; và hồi máu cho nhân vật gây DMG trong đội gần đó.</t>
         </is>
       </c>
     </row>
@@ -25538,7 +25538,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Verina: Hướng dẫn Resonance Liberation &lt;color=#d4bf5f&gt;Photosynthesis Mark&lt;/color&gt;</t>
+          <t>Verina: Hướng dẫn Resonance Liberation &lt;color=#d4bf5f&gt;Dấu Hiệu Quang Hợp&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -25603,7 +25603,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để thực hiện Đòn Lao Không Trung, gây &lt;color=#f9ff4a&gt;Spectro DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để thực hiện Đòn Lao Không Trung, gây &lt;color=#f9ff4a&gt;Sát Thương Spectro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -25668,7 +25668,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Verina: &lt;color=#d4bf5f&gt;Mid-Air Heavy Attack&lt;/color&gt;</t>
+          <t>Verina: &lt;color=#d4bf5f&gt;Hướng dẫn Tấn Công Mạnh Giữa Không Trung&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -25798,7 +25798,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Giải Phóng Enhanced Resonance</t>
+          <t>Resonance Liberation Cường Hóa</t>
         </is>
       </c>
     </row>
@@ -25863,7 +25863,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Buling: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Buling: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -25928,7 +25928,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt; và lần lượt nhận được &lt;color=#d4bf5f&gt;Trigram - Mountain&lt;/color&gt; và &lt;color=#d4bf5f&gt;Trigram - Thunder&lt;/color&gt;.</t>
+          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt; và lần lượt nhận được &lt;color=#d4bf5f&gt;Quẻ - Sơn&lt;/color&gt; và &lt;color=#d4bf5f&gt;Quẻ - Lôi&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -25993,7 +25993,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Buling: &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt; 1</t>
+          <t>Buling: &lt;color=#d4bf5f&gt;Hướng dẫn Heavy Attack&lt;/color&gt; 1</t>
         </is>
       </c>
     </row>
@@ -26058,7 +26058,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Sau khi tích lũy &lt;color=Highlight&gt;Trigrams&lt;/color&gt; bằng Basic Attack, giữ Normal Attack để tiêu hao &lt;color=#d4bf5f&gt;Trigram - Mountain&lt;/color&gt; và &lt;color=#d4bf5f&gt;Trigram - Thunder&lt;/color&gt; nhằm thực hiện &lt;color=Highlight&gt;Heavy Attack - Mountain Over Thunder&lt;/color&gt;. Thu được &lt;color=Highlight&gt;Minor Yang&lt;/color&gt; sau khi hành động thành công.</t>
+          <t>Sau khi tích lũy &lt;color=Highlight&gt;Bát Quái&lt;/color&gt; bằng Đòn Basic Attack, giữ Đòn Normal Attack để tiêu hao &lt;color=#d4bf5f&gt;Bát Quái - Sơn&lt;/color&gt; và &lt;color=#d4bf5f&gt;Bát Quái - Lôi&lt;/color&gt; nhằm thực hiện &lt;color=Highlight&gt;Đòn Heavy Attack - Sơn Lôi Trùng Phục&lt;/color&gt;. Thu được &lt;color=Highlight&gt;Thiếu Dương&lt;/color&gt; sau khi hành động thành công.</t>
         </is>
       </c>
     </row>
@@ -26123,7 +26123,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để thực hiện Đòn Lao Xuống, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;. Khi trúng mục tiêu, nhận 1 &lt;color=#d4bf5f&gt;Trigram - Thunder&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để thực hiện Đòn Lao Xuống, gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;. Khi trúng mục tiêu, nhận 1 &lt;color=#d4bf5f&gt;Quẻ - Sấm&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -26188,7 +26188,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Buling: &lt;color=#d4bf5f&gt;Resonance Skill&lt;/color&gt;</t>
+          <t>Buling: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Skill&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -26253,7 +26253,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Skill để gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;, đồng thời kéo các mục tiêu xung quanh vào trong một lúc, nhận được &lt;color=#d4bf5f&gt;Trigram - Thunder&lt;/color&gt;. {Cus:Ipt,Touch=Touch PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau kỹ năng này để tung ra &lt;color=Highlight&gt;Basic Attack Stage 4&lt;/color&gt;.</t>
+          <t>Kích hoạt Resonance Skill để gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;, đồng thời kéo các mục tiêu xung quanh vào trong một lúc, nhận được &lt;color=#d4bf5f&gt;Quẻ - Sấm&lt;/color&gt;. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Đòn Normal Attack&lt;/color&gt; ngay sau kỹ năng này để tung ra &lt;color=Highlight&gt;Đòn Basic Attack Cấp 4&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -26318,7 +26318,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Buling: &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt; 2</t>
+          <t>Buling: &lt;color=#d4bf5f&gt;Hướng dẫn Heavy Attack&lt;/color&gt; 2</t>
         </is>
       </c>
     </row>
@@ -26383,7 +26383,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau Resonance Skill để thi triển &lt;color=Highlight&gt;Basic Attack Stage 4&lt;/color&gt; và nhận 2 &lt;color=#d4bf5f&gt;Trigrams - Thunder&lt;/color&gt;. Giữ Normal Attack để tiêu hao 2 &lt;color=#d4bf5f&gt;Trigrams - Thunder&lt;/color&gt; và thi triển &lt;color=Highlight&gt;Heavy Attack - Twin Thunders&lt;/color&gt;. Hoàn thành hành động sẽ nhận &lt;color=Highlight&gt;Minor Yin&lt;/color&gt;.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Đòn Normal Attack&lt;/color&gt; ngay sau Resonance Skill để thi triển &lt;color=Highlight&gt;Giai Đoạn 4 Đòn Basic Attack&lt;/color&gt; và nhận 2 &lt;color=#d4bf5f&gt;Quẻ - Lôi&lt;/color&gt;. Giữ Đòn Normal Attack để tiêu hao 2 &lt;color=#d4bf5f&gt;Quẻ - Lôi&lt;/color&gt; và thi triển &lt;color=Highlight&gt;Đòn Tấn Công Mạnh - Song Lôi&lt;/color&gt;. Hoàn thành hành động sẽ nhận &lt;color=Highlight&gt;Âm Tiêu&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -26448,7 +26448,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Buling: &lt;color=#d4bf5f&gt;Enhanced Resonance Liberation&lt;/color&gt;</t>
+          <t>Buling: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Liberation Nâng Cao&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -26515,7 +26515,7 @@
       <c r="M399" t="inlineStr">
         <is>
           <t>"Thay đổi
-Khi Buling đạt được &lt;color=Highlight&gt;Minor Yin&lt;/color&gt; và &lt;color=Highlight&gt;Minor Yang&lt;/color&gt;, cô ấy bước vào trạng thái &lt;color=Highlight&gt;Yin-Yang Balance&lt;/color&gt;, thay thế &lt;color=Highlight&gt;Resonance Liberation - Flashing Thunder Spell&lt;/color&gt; bằng &lt;color=Highlight&gt;Resonance Liberation - Flashing Thunder Spell: Harmony&lt;/color&gt;. Khi sử dụng kỹ năng, một &lt;color=Highlight&gt;Five Thunders Spell Array&lt;/color&gt; sẽ xuất hiện tại khu vực mục tiêu, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt; và định kỳ áp dụng hiệu ứng &lt;color=Highlight&gt;Electro Flare&lt;/color&gt; lên tất cả mục tiêu trong phạm vi."</t>
+Khi Buling đạt được &lt;color=Highlight&gt;Âm Nhỏ&lt;/color&gt; và &lt;color=Highlight&gt;Dương Nhỏ&lt;/color&gt;, cô ấy bước vào trạng thái &lt;color=Highlight&gt;Âm Dương Cân Bằng&lt;/color&gt;, thay thế &lt;color=Highlight&gt;Resonance Liberation - Phép Thuật Sấm Chớp&lt;/color&gt; bằng &lt;color=Highlight&gt;Resonance Liberation - Phép Thuật Sấm Chớp: Hòa Điệu&lt;/color&gt;. Khi sử dụng kỹ năng, một &lt;color=Highlight&gt;Bát Quái Trận Pháp Ngũ Lôi&lt;/color&gt; sẽ xuất hiện tại khu vực mục tiêu, gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt; và định kỳ áp dụng hiệu ứng &lt;color=Highlight&gt;Lôi Quang&lt;/color&gt; lên tất cả mục tiêu trong phạm vi."</t>
         </is>
       </c>
     </row>
@@ -26580,7 +26580,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Nhấn {Cus:Ipt,Touch=Ấn PC=press Gamepad=press} Normal Attack liên tiếp để thực hiện &lt;color=Highlight&gt;Basic Attack&lt;/color&gt;, &lt;color=Highlight&gt;Rending Lunge&lt;/color&gt;, &lt;color=Highlight&gt;Death Snip&lt;/color&gt; và &lt;color=Highlight&gt;Thread Withdrawn&lt;/color&gt; theo thứ tự, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Đòn Thường liên tiếp để thực hiện &lt;color=Highlight&gt;Đòn Cơ Bản&lt;/color&gt;, &lt;color=Highlight&gt;Rending Lunge&lt;/color&gt;, &lt;color=Highlight&gt;Death Snip&lt;/color&gt; và &lt;color=Highlight&gt;Thread Withdrawn&lt;/color&gt; theo thứ tự, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -26645,7 +26645,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Chisa: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Chisa: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -26711,8 +26711,8 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Nhảy lên không và tiêu hao STA để tấn công mục tiêu, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;. 
-{Cus:Ipt,Touch=Touch PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng kỹ năng này để thi triển &lt;color=Highlight&gt;Hanging Finality&lt;/color&gt;.</t>
+          <t>Nhảy lên không và tiêu hao STA để tấn công mục tiêu, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;. 
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Đòn Normal Attack&lt;/color&gt; ngay sau khi sử dụng kỹ năng này để thi triển &lt;color=Highlight&gt;Hanging Finality&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -26777,7 +26777,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Chisa: Hướng dẫn &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt; - Combo</t>
+          <t>Chisa: Hướng dẫn &lt;color=#d4bf5f&gt;Đòn Tấn Công Mạnh&lt;/color&gt; - Combo</t>
         </is>
       </c>
     </row>
@@ -26843,8 +26843,8 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Giữ Gamepad=Giữ} &lt;color=Highlight&gt;Dodge&lt;/color&gt; sau khi tung &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; trước khi tiếp đất để thi triển &lt;color=Highlight&gt;Lifethread - Glide&lt;/color&gt;.
-Trong kỹ năng, giữ &lt;color=Highlight&gt;Dodge&lt;/color&gt; để lướt một đoạn ngắn trên vũ khí.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Né Tránh&lt;/color&gt; sau khi tung &lt;color=Highlight&gt;Đòn Tấn Công Mạnh&lt;/color&gt; trước khi tiếp đất để thi triển &lt;color=Highlight&gt;Sợi Sinh Mệnh - Lướt&lt;/color&gt;.
+Trong kỹ năng, giữ &lt;color=Highlight&gt;Né Tránh&lt;/color&gt; để lướt một đoạn ngắn trên vũ khí.</t>
         </is>
       </c>
     </row>
@@ -26909,7 +26909,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Thực hiện &lt;color=Highlight&gt;Mid-air Heavy Attack&lt;/color&gt; bằng cách giữ &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; sau khi kích hoạt &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; khi vẫn còn trên không trước khi hạ cánh.</t>
+          <t>Thực hiện &lt;color=Highlight&gt;Đòn Heavy Attack Trên Không&lt;/color&gt; bằng cách giữ &lt;color=Highlight&gt;Đòn Normal Attack&lt;/color&gt; sau khi kích hoạt &lt;color=Highlight&gt;Đòn Heavy Attack&lt;/color&gt; khi vẫn còn trên không trước khi hạ cánh.</t>
         </is>
       </c>
     </row>
@@ -26974,7 +26974,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Chisa: Hướng dẫn &lt;color=#d4bf5f&gt;Mid-air Heavy Attack&lt;/color&gt;</t>
+          <t>Chisa: Hướng dẫn &lt;color=#d4bf5f&gt;Đòn Tấn Công Mạnh Trên Không&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -27039,7 +27039,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để thực hiện Đòn Lao, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để thực hiện Đòn Lao, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -27105,8 +27105,8 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; và &lt;color=Highlight&gt;mark&lt;/color&gt; mục tiêu.
-Sau khi sử dụng kỹ năng này, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trên mặt đất hoặc sử dụng &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; giữa không trung để thi triển &lt;color=Highlight&gt;Rending Lunge&lt;/color&gt;.</t>
+          <t>Gây &lt;color=Dark&gt;DMG Havoc&lt;/color&gt; và &lt;color=Highlight&gt;đánh dấu&lt;/color&gt; mục tiêu.
+Sau khi sử dụng kỹ năng này, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trên mặt đất hoặc sử dụng &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; giữa không trung để thi triển &lt;color=Highlight&gt;Đòn Xé Rách&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -27171,7 +27171,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Chisa: Hướng dẫn &lt;color=#d4bf5f&gt;Resonance Skill&lt;/color&gt; Trên Mặt Đất</t>
+          <t>Chisa: Hướng dẫn &lt;color=#d4bf5f&gt;Combo Resonance Skill&lt;/color&gt; Trên Mặt Đất</t>
         </is>
       </c>
     </row>
@@ -27237,8 +27237,8 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; và &lt;color=Highlight&gt;mark&lt;/color&gt; mục tiêu.
-Sau khi sử dụng kỹ năng này, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trên mặt đất hoặc sử dụng &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; giữa không trung để thi triển &lt;color=Highlight&gt;Rending Lunge&lt;/color&gt;.</t>
+          <t>Gây &lt;color=Dark&gt;DMG Havoc&lt;/color&gt; và &lt;color=Highlight&gt;đánh dấu&lt;/color&gt; mục tiêu.
+Sau khi sử dụng kỹ năng này, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trên mặt đất hoặc sử dụng &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; giữa không trung để thi triển &lt;color=Highlight&gt;Đòn Xé Rách&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -27303,7 +27303,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Chisa: Hướng dẫn &lt;color=#d4bf5f&gt;Resonance Skill&lt;/color&gt; Trên Không</t>
+          <t>Chisa: Hướng dẫn &lt;color=#d4bf5f&gt;Combo Resonance Skill&lt;/color&gt; Trên Không</t>
         </is>
       </c>
     </row>
@@ -27368,7 +27368,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Skill Cộng hưởng Ground</t>
+          <t>Kỹ năng Cộng hưởng Mặt đất</t>
         </is>
       </c>
     </row>
@@ -27500,8 +27500,8 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt; đầy, có thể sử dụng &lt;color=Highlight&gt;Enhanced Resonance Skill&lt;/color&gt;.
-Gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; và &lt;color=Highlight&gt;mark&lt;/color&gt; mục tiêu.
+          <t>Khi &lt;color=Highlight&gt;Đồng Hồ Forte&lt;/color&gt; đầy, có thể sử dụng &lt;color=Highlight&gt;Resonance Skill Tăng Cường&lt;/color&gt;.
+Gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; và &lt;color=Highlight&gt;đánh dấu&lt;/color&gt; mục tiêu.
 Sử dụng kỹ năng này sẽ đưa Chisa vào &lt;color=Highlight&gt;Chainsaw Mode&lt;/color&gt;.</t>
         </is>
       </c>
@@ -27567,7 +27567,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Chisa: Hướng dẫn &lt;color=#d4bf5f&gt;Enhanced Resonance Skill&lt;/color&gt; - Combo</t>
+          <t>Chisa: Hướng dẫn &lt;color=#d4bf5f&gt;Resonance Skill Nâng Cao&lt;/color&gt; - Combo</t>
         </is>
       </c>
     </row>
@@ -27632,7 +27632,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Giữ &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; trong khi thi triển &lt;color=Highlight&gt;enhanced Resonance Skill&lt;/color&gt; để liên tục hút các mục tiêu xung quanh. Thả nút &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; hoặc giữ trong một khoảng thời gian nhất định để thi triển &lt;color=Highlight&gt;ChainsawMode Basic Attack Stage 1&lt;/color&gt;.</t>
+          <t>Giữ &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; trong khi thi triển &lt;color=Highlight&gt;Resonance Skill được tăng cường&lt;/color&gt; để liên tục hút các mục tiêu xung quanh. Thả nút &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; hoặc giữ trong một khoảng thời gian nhất định để thi triển &lt;color=Highlight&gt;Đòn Basic Attack Cưa Xích Giai Đoạn 1&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -27697,7 +27697,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Chisa: Hướng dẫn &lt;color=#d4bf5f&gt;Enhanced Resonance Skill&lt;/color&gt; - Giữ</t>
+          <t>Chisa: Hướng dẫn &lt;color=#d4bf5f&gt;Resonance Skill Nâng Cao&lt;/color&gt; - Giữ</t>
         </is>
       </c>
     </row>
@@ -27763,8 +27763,8 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; và phục hồi HP cho tất cả Resonators gần đó trong đội. 
-Kích hoạt kỹ năng này sẽ đưa Chisa vào &lt;color=Highlight&gt;Enhanced Chainsaw Mode&lt;/color&gt;, nơi Hệ Số Sát Thương của &lt;color=Highlight&gt;Chainsaw Mode Basic Attack&lt;/color&gt; và &lt;color=Highlight&gt;Chainsaw Mode Finisher Attack&lt;/color&gt; được tăng đáng kể.</t>
+          <t>Gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; và phục hồi HP cho tất cả Resonator gần đó trong đội. 
+Kích hoạt kỹ năng này sẽ đưa Chisa vào &lt;color=Highlight&gt;Chế Độ Cưa Máy Tăng Cường&lt;/color&gt;, nơi Hệ Số Sát Thương của &lt;color=Highlight&gt;Đòn Cơ Bản Chế Độ Cưa Máy&lt;/color&gt; và &lt;color=Highlight&gt;Đòn Kết Thúc Chế Độ Cưa Máy&lt;/color&gt; được tăng đáng kể.</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Kỹ Năng Enhanced Resonance</t>
+          <t>Resonance Skill Cường Hóa</t>
         </is>
       </c>
     </row>
@@ -27959,7 +27959,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Kỹ Năng Enhanced Resonance</t>
+          <t>Resonance Skill Cường Hóa</t>
         </is>
       </c>
     </row>
@@ -28089,7 +28089,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Nhấn {Cus:Ipt,Touch=Ấn PC=press Gamepad=press} Normal Attack liên tiếp để thực hiện tối đa 3 đòn tấn công liên tiếp, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Đòn Thường liên tiếp để thực hiện tối đa 3 đòn tấn công liên tiếp, gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Lynae: Hướng dẫn &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Lynae: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt; Hướng Dẫn</t>
         </is>
       </c>
     </row>
@@ -28219,7 +28219,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Khi ở trên không, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack để tiêu hao Thể Lực và thực hiện Đòn Lao Xuống, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.</t>
+          <t>Khi ở trên không, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Đòn Normal Attack để tiêu hao STA và thực hiện Đòn Lao Xuống, gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -28284,7 +28284,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Nhấn {Cus:Ipt,Touch=Ấn PC=press Gamepad=press} Resonance Skill để lao về phía trước và gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Resonance Skill để lao về phía trước và gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -28349,7 +28349,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Lynae: Hướng dẫn &lt;color=#d4bf5f&gt;Resonance Skill&lt;/color&gt;</t>
+          <t>Lynae: &lt;color=#d4bf5f&gt;Resonance Skill&lt;/color&gt; Hướng Dẫn</t>
         </is>
       </c>
     </row>
@@ -28414,7 +28414,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Trong trạng thái &lt;color=Highlight&gt;Optical Sampling Stage&lt;/color&gt;, khi &lt;color=Highlight&gt;Overflow&lt;/color&gt; đạt tối đa, giữ Normal Attack để vào trạng thái nạp, trong đó Lynae liên tục chuyển hóa &lt;color=Highlight&gt;Overflow&lt;/color&gt; thành &lt;color=Highlight&gt;Lumiflow&lt;/color&gt;. Thả Normal Attack để lao về phía mục tiêu, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.</t>
+          <t>Trong trạng thái &lt;color=Highlight&gt;Giai Đoạn Lấy Mẫu Quang Học&lt;/color&gt;, khi &lt;color=Highlight&gt;Tràn Dòng&lt;/color&gt; đạt tối đa, giữ Normal Attack để vào trạng thái nạp, trong đó Lynae liên tục chuyển hóa &lt;color=Highlight&gt;Tràn Dòng&lt;/color&gt; thành &lt;color=Highlight&gt;Dòng Sáng&lt;/color&gt;. Thả Normal Attack để lao về phía mục tiêu, gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -28479,7 +28479,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Lynae: Hướng dẫn &lt;color=#d4bf5f&gt;Basic Attack - Spark Collision&lt;/color&gt;</t>
+          <t>Lynae: &lt;color=#d4bf5f&gt;Basic Attack - Va Chạm Lóe Sáng&lt;/color&gt; Hướng Dẫn</t>
         </is>
       </c>
     </row>
@@ -28544,7 +28544,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Trong &lt;color=Highlight&gt;Kaleidoscopic Parade&lt;/color&gt;, giữ Resonance Skill để thoát trạng thái.</t>
+          <t>Trong &lt;color=Highlight&gt;Diễu Hành Muôn Màu&lt;/color&gt;, giữ Resonance Skill để thoát trạng thái.</t>
         </is>
       </c>
     </row>
@@ -28609,7 +28609,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Trong trạng thái &lt;color=Highlight&gt;Kaleidoscopic Parade&lt;/color&gt;, &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; của Lynae sẽ được thay thế bằng &lt;color=Highlight&gt;Kaleidoscopic Parade - Basic Attack&lt;/color&gt;. {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack liên tiếp để thực hiện tối đa 5 đòn đánh liên tục, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.</t>
+          <t>Trong trạng thái &lt;color=Highlight&gt;Diễu Hành Sắc Màu&lt;/color&gt;, &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt; của Lynae sẽ được thay thế bằng &lt;color=Highlight&gt;Diễu Hành Sắc Màu - Đòn Basic Attack&lt;/color&gt;. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack liên tiếp để thực hiện tối đa 5 đòn đánh liên tục, gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -28674,7 +28674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Lynae: Hướng dẫn &lt;color=#d4bf5f&gt;Kaleidoscopic Parade - Basic Attack&lt;/color&gt;</t>
+          <t>Lynae: &lt;color=#d4bf5f&gt;Diễu Hành Muôn Màu - Basic Attack&lt;/color&gt; Hướng Dẫn</t>
         </is>
       </c>
     </row>
@@ -28739,7 +28739,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Nhấn {Cus:Ipt,Touch=Ấn PC=press Gamepad=press} Nhảy để thực hiện tối đa 3 giai đoạn của &lt;color=Highlight&gt;Basic Attack - Polychrome Leap&lt;/color&gt; bằng cách tiêu hao &lt;color=Highlight&gt;Lumiflow&lt;/color&gt;, hồi phục &lt;color=Highlight&gt;True Color&lt;/color&gt;. Khi &lt;color=Highlight&gt;True Color&lt;/color&gt; đầy, {Cus:Ipt,Touch=ấn PC=press Gamepad=press} Normal Attack hoặc Resonance Skill để tung &lt;color=Highlight&gt;Basic Attack - Iridescent Splash&lt;/color&gt; hoặc &lt;color=Highlight&gt;Basic Attack - Visual Impact&lt;/color&gt;.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Nhảy để thực hiện tối đa 3 giai đoạn của &lt;color=Highlight&gt;Đòn Cơ Bản - Polychrome Leap&lt;/color&gt; bằng cách tiêu hao &lt;color=Highlight&gt;Lumiflow&lt;/color&gt;, hồi phục &lt;color=Highlight&gt;True Color&lt;/color&gt;. Khi &lt;color=Highlight&gt;True Color&lt;/color&gt; đầy, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Đòn Thường hoặc Resonance Skill để tung &lt;color=Highlight&gt;Đòn Cơ Bản - Iridescent Splash&lt;/color&gt; hoặc &lt;color=Highlight&gt;Đòn Cơ Bản - Visual Impact&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -28804,7 +28804,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Lynae: Hướng dẫn &lt;color=#d4bf5f&gt;Basic Attack - Polychrome Leap&lt;/color&gt;</t>
+          <t>Lynae: &lt;color=#d4bf5f&gt;Basic Attack - Nhảy Đa Sắc&lt;/color&gt; Hướng Dẫn</t>
         </is>
       </c>
     </row>
@@ -28869,7 +28869,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Khi Lynae ở trạng thái &lt;color=Highlight&gt;Kaleidoscopic Parade&lt;/color&gt; và trên mặt đất, cô liên tục tấn công mục tiêu bằng cách tiêu hao STA, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;. Khi thả nút Normal Attack, Lynae tung chiêu &lt;color=Highlight&gt;Kaleidoscopic Parade - Graffiti Blast&lt;/color&gt;, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.</t>
+          <t>Khi Lynae ở trạng thái &lt;color=Highlight&gt;Kaleidoscopic Parade&lt;/color&gt; và trên mặt đất, cô liên tục tấn công mục tiêu bằng cách tiêu hao STA, gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;. Khi thả nút Normal Attack, Lynae tung chiêu &lt;color=Highlight&gt;Kaleidoscopic Parade - Graffiti Blast&lt;/color&gt;, gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -28934,7 +28934,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Lynae: Hướng dẫn &lt;color=#d4bf5f&gt;Kaleidoscopic Parade - Ground Heavy Attack&lt;/color&gt;</t>
+          <t>Lynae: &lt;color=#d4bf5f&gt;Diễu Hành Muôn Màu - Tấn Công Mạnh Trên Mặt Đất&lt;/color&gt; Hướng Dẫn</t>
         </is>
       </c>
     </row>
@@ -28999,7 +28999,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Trong trạng thái &lt;color=Highlight&gt;Kaleidoscopic Parade&lt;/color&gt;, giữ Normal Attack giữa không trung để tấn công mục tiêu, tiêu hao STA và gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.</t>
+          <t>Trong trạng thái &lt;color=Highlight&gt;Diễu Hành Sắc Màu&lt;/color&gt;, giữ Normal Attack giữa không trung để tấn công mục tiêu, tiêu hao STA và gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Lynae: Hướng dẫn &lt;color=#d4bf5f&gt;Kaleidoscopic Parade - Mid-air Heavy Attack&lt;/color&gt;</t>
+          <t>Lynae: &lt;color=#d4bf5f&gt;Diễu Hành Muôn Màu - Tấn Công Mạnh Trên Không&lt;/color&gt; Hướng Dẫn</t>
         </is>
       </c>
     </row>
@@ -29129,7 +29129,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;. Khi sử dụng kỹ năng này, tăng sát thương cho tất cả Resonators gần đó trong đội.</t>
+          <t>Gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;. Khi sử dụng kỹ năng này, tăng DMG cho tất cả Resonator gần đó trong đội.</t>
         </is>
       </c>
     </row>
@@ -29194,7 +29194,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Lynae: Hướng dẫn &lt;color=#d4bf5f&gt;Resonance Liberation&lt;/color&gt;</t>
+          <t>Lynae: &lt;color=#d4bf5f&gt;Resonance Liberation&lt;/color&gt; Hướng Dẫn</t>
         </is>
       </c>
     </row>
@@ -29259,7 +29259,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Vung lưỡi kiếm khổng lồ và tung ra tối đa 4 đòn liên tiếp, gây &lt;color=#e649a6&gt;Havoc DMG&lt;/color&gt;.</t>
+          <t>Vung lưỡi kiếm khổng lồ và tung ra tối đa 4 đòn liên tiếp, gây &lt;color=#e649a6&gt;Sát Thương Havoc&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -29324,7 +29324,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Taoqi: Hướng dẫn &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Taoqi: Hướng dẫn &lt;color=#d4bf5f&gt;Đòn Basic Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -29389,7 +29389,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Tiêu hao STA và进入 trạng thái &lt;color=#f4d582&gt;Rocksteady Defense&lt;/color&gt;. Thả nút Heavy Attack để kết thúc &lt;color=#f4d582&gt;Rocksteady Defense&lt;/color&gt; và lập tức tung đòn tấn công, gây &lt;color=#e649a6&gt;Havoc DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA và进入 trạng thái &lt;color=#f4d582&gt;Phòng Thủ Kiên Cố&lt;/color&gt;. Thả nút Đòn Nặng để kết thúc &lt;color=#f4d582&gt;Phòng Thủ Kiên Cố&lt;/color&gt; và lập tức tung đòn tấn công, gây &lt;color=#e649a6&gt;Sát Thương Havoc&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -29454,7 +29454,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Taoqi: Hướng dẫn &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt;</t>
+          <t>Taoqi: Hướng dẫn &lt;color=#d4bf5f&gt;Đòn tấn công mạnh&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -29519,7 +29519,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để thực hiện Đòn Lao Không Trung, gây &lt;color=#e649a6&gt;Havoc DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để thực hiện Đòn Lao Không Trung, gây &lt;color=#e649a6&gt;Sát Thương Havoc&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -29584,7 +29584,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Triệu hồi "Defense Vững Chắc", gây &lt;color=#e649a6&gt;Havoc DMG&lt;/color&gt; lên các mục tiêu xung quanh và tạo ra 3 &lt;color=#f4d582&gt;Rocksteady Shield&lt;/color&gt;. Các đòn tấn công vào thời điểm này sẽ kích hoạt &lt;color=#f4d582&gt;Strategic Parry&lt;/color&gt; để phản công lại mục tiêu.</t>
+          <t>Triệu hồi "Phòng Ngự Vững Chắc", gây &lt;color=#e649a6&gt;Sát Thương Havoc&lt;/color&gt; lên các mục tiêu xung quanh và tạo ra 3 &lt;color=#f4d582&gt;Khiên Đá Kiên Cố&lt;/color&gt;. Các đòn tấn công vào thời điểm này sẽ kích hoạt &lt;color=#f4d582&gt;Phản Đòn Chiến Thuật&lt;/color&gt; để phản công lại mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -29649,7 +29649,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Taoqi: Hướng dẫn Resonance Skill</t>
+          <t>Taoqi: Resonance Skill Tutorial</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -29779,7 +29779,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Dựa vào Phòng Ngự của Taoqi, phóng đòn tấn công vào mục tiêu, gây &lt;color=#e649a6&gt;Havoc DMG&lt;/color&gt; và làm chậm các mục tiêu xung quanh.</t>
+          <t>Dựa vào Phòng Ngự của Taoqi, phóng đòn tấn công vào mục tiêu, gây &lt;color=#e649a6&gt;Sát Thương Havoc&lt;/color&gt; và làm chậm các mục tiêu xung quanh.</t>
         </is>
       </c>
     </row>
@@ -29844,7 +29844,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Taoqi: Hướng dẫn Resonance Liberation</t>
+          <t>Taoqi: Resonance Liberation Tutorial</t>
         </is>
       </c>
     </row>
@@ -29910,7 +29910,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Focus vào Defense và giảm sát thương khi ở trạng thái &lt;color=#f4d582&gt;Rocksteady Defense&lt;/color&gt;.
+          <t>Tập trung vào Phòng Ngự và giảm DMG khi ở trạng thái &lt;color=#f4d582&gt;Rocksteady Defense&lt;/color&gt;.
 Trong trạng thái &lt;color=#f4d582&gt;Rocksteady Defense&lt;/color&gt;, khi bị tấn công hoặc hoàn thành nạp, kích hoạt &lt;color=#f4d582&gt;Strategic Parry&lt;/color&gt;, phản công mục tiêu và gây &lt;color=#e649a6&gt;Havoc DMG&lt;/color&gt;.</t>
         </is>
       </c>
@@ -29976,7 +29976,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Taoqi: &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt; - &lt;color=#d4bf5f&gt;Strategic Parry&lt;/color&gt;</t>
+          <t>Taoqi: &lt;color=#d4bf5f&gt;Hướng dẫn Tấn Công Mạnh&lt;/color&gt; - &lt;color=#d4bf5f&gt;Phản Đòn Chiến Thuật&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -30041,7 +30041,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Khi &lt;color=#f4d582&gt;Heavy Attack: Strategic Parry&lt;/color&gt; kích hoạt thành công, thực hiện tối đa ba đòn tấn công tiếp theo, gây &lt;color=#e649a6&gt;Havoc DMG&lt;/color&gt;, được tính là sát thương Basic Attack. Mỗi đòn tiếp theo trúng mục tiêu sẽ tiêu hao "Độ Chuẩn Xác Giải Quyết" để tạo khiên.</t>
+          <t>Khi &lt;color=#f4d582&gt;Đòn Heavy Attack: Phản Đòn Chiến Thuật&lt;/color&gt; kích hoạt thành công, thực hiện tối đa ba đòn tấn công tiếp theo, gây &lt;color=#e649a6&gt;Sát Thương Havoc&lt;/color&gt;, được tính là DMG Đòn Basic Attack. Mỗi đòn tiếp theo trúng mục tiêu sẽ tiêu hao "Độ Chuẩn Xác Giải Quyết" để tạo khiên.</t>
         </is>
       </c>
     </row>
@@ -30106,7 +30106,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Taoqi: Hướng dẫn Forte Circuit - &lt;color=#f4d582&gt;Timed Counters&lt;/color&gt;</t>
+          <t>Taoqi: Hướng dẫn Forte Circuit - &lt;color=#f4d582&gt;Phản Đòn Đúng Lúc&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -30171,7 +30171,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 3 đòn tấn công liên tiếp, gây &lt;color=#e649a6&gt;Havoc DMG&lt;/color&gt;.</t>
+          <t>Thực hiện tối đa 3 đòn tấn công liên tiếp, gây &lt;color=#e649a6&gt;Sát Thương Hỗn Loạn&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -30236,7 +30236,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Danjin: Hướng dẫn &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Danjin: Hướng dẫn &lt;color=#d4bf5f&gt;Đòn Basic Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -30366,7 +30366,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Danjin: Hướng dẫn Resonance Skill</t>
+          <t>Danjin: Resonance Skill Tutorial</t>
         </is>
       </c>
     </row>
@@ -30431,7 +30431,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -30496,7 +30496,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Danjin tung đòn tấn công, gây &lt;color=#e649a6&gt;Havoc DMG&lt;/color&gt; và nhận được "Hoa Hồng Đỏ".</t>
+          <t>Danjin tung đòn tấn công, gây &lt;color=#e649a6&gt;Sát Thương Havoc&lt;/color&gt; và nhận được "Hoa Hồng Đỏ".</t>
         </is>
       </c>
     </row>
@@ -30561,7 +30561,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Danjin: Hướng dẫn Resonance Skill &lt;color=#d4bf5f&gt;Carmine Gleam&lt;/color&gt;</t>
+          <t>Danjin: Hướng dẫn Resonance Skill &lt;color=#d4bf5f&gt;Ánh Hồng Thạch&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -30626,7 +30626,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Danjin: Hướng dẫn Resonance Skill &lt;color=#d4bf5f&gt;Crimson Erosion&lt;/color&gt;</t>
+          <t>Danjin: Hướng dẫn Resonance Skill &lt;color=#d4bf5f&gt;Xói Mòn Đỏ Thẫm&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -30691,7 +30691,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Sau khi dùng &lt;color=#f4d582&gt;Crimson Fragment&lt;/color&gt;, sử dụng &lt;color=#f4d582&gt;Basic Attack 3&lt;/color&gt; để thực hiện tối đa 3 đòn Xung Huyết, gây &lt;color=#e649a6&gt;Havoc DMG&lt;/color&gt;.</t>
+          <t>Sau khi dùng &lt;color=#f4d582&gt;Đòn Basic Attack 3&lt;/color&gt;, sử dụng &lt;color=#f4d582&gt;Mảnh Đỏ Thẫm&lt;/color&gt; để thực hiện tối đa 3 đòn Xung Huyết, gây &lt;color=#e649a6&gt;Sát Thương Havoc&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -30756,7 +30756,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Danjin: Hướng dẫn Resonance Skill &lt;color=#d4bf5f&gt;Sanguine Pulse&lt;/color&gt;</t>
+          <t>Danjin: Hướng dẫn Resonance Skill &lt;color=#d4bf5f&gt;Xung Huyết&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -30821,7 +30821,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Kết hợp Forte của bạn với lưỡi kiếm và tiêu hao STA để tung ra những đòn tấn công liên tiếp, gây &lt;color=#e649a6&gt;Havoc DMG&lt;/color&gt;.</t>
+          <t>Kết hợp Forte của bạn với lưỡi kiếm và tiêu hao STA để tung ra những đòn tấn công liên tiếp, gây &lt;color=#e649a6&gt;Sát Thương Havoc&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -30886,7 +30886,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Hướng dẫn &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt; của Danjin</t>
+          <t>Hướng dẫn &lt;color=#d4bf5f&gt;Tấn Công Mạnh&lt;/color&gt; của Danjin</t>
         </is>
       </c>
     </row>
@@ -30951,7 +30951,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Khi "Hoa Hồng Đỏ" vượt quá 60, tung đòn tấn công mạnh hơn, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; và hồi HP. Khi "Hoa Hồng Đỏ" vượt quá 120, đòn tấn công này gây thêm sát thương. Trong một khoảng thời gian sau khi sử dụng Heavy Attack: Chaoscleave, dùng &lt;color=#f4d582&gt;Basic Attack&lt;/color&gt; để phóng &lt;color=#d4bf5f&gt;Heavy Attack: Scatterbloom&lt;/color&gt;, gây &lt;color=#e649a6&gt;Havoc DMG&lt;/color&gt;.</t>
+          <t>Khi "Hoa Hồng Đỏ" vượt quá 60, tung đòn tấn công mạnh hơn, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; và hồi HP. Khi "Hoa Hồng Đỏ" vượt quá 120, đòn tấn công này gây thêm DMG. Trong một khoảng thời gian sau khi sử dụng Đòn Heavy Attack: Chaoscleave, dùng &lt;color=#f4d582&gt;Basic Attack&lt;/color&gt; để phóng &lt;color=#d4bf5f&gt;Đòn Heavy Attack: Scatterbloom&lt;/color&gt;, gây &lt;color=#e649a6&gt;Sát Thương Havoc&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -31016,7 +31016,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Danjin: Hướng dẫn Forte Circuit &lt;color=#d4bf5f&gt;Heavy Attack: Chaoscleave&lt;/color&gt;</t>
+          <t>Danjin: Hướng dẫn Forte Circuit &lt;color=#d4bf5f&gt;Đòn Heavy Attack: Chaoscleave&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -31081,7 +31081,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để thực hiện Đòn Lao Không Trung, gây &lt;color=#e649a6&gt;Havoc DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để thực hiện Đòn Lao Không Trung, gây &lt;color=#e649a6&gt;Sát Thương Havoc&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -31146,7 +31146,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Vung hai lưỡi kiếm liên tiếp vào mục tiêu, thực hiện nhiều đòn tấn công nhanh liên tục và một đòn tấn công bùng nổ, gây &lt;color=#e649a6&gt;Havoc DMG&lt;/color&gt;.</t>
+          <t>Vung hai lưỡi kiếm liên tiếp vào mục tiêu, thực hiện nhiều đòn tấn công nhanh liên tục và một đòn tấn công bùng nổ, gây &lt;color=#e649a6&gt;Sát Thương Havoc&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -31211,7 +31211,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Danjin: Hướng dẫn Resonance Liberation</t>
+          <t>Danjin: Resonance Liberation Tutorial</t>
         </is>
       </c>
     </row>
@@ -31276,7 +31276,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 5 đòn tấn công liên tiếp, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.</t>
+          <t>Thực hiện tối đa 5 đòn tấn công liên tiếp, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -31341,7 +31341,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Rover: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Rover: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -31406,7 +31406,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để thi triển Đòn Lao Xuống từ trên không, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để thi triển Đòn Lao Xuống từ trên không, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -31471,7 +31471,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để tấn công mục tiêu, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;. Trong thời gian ngắn sau khi thực hiện Heavy Attack, dùng Basic Attack để kích hoạt Stage 4 Basic Attack.</t>
+          <t>Tiêu hao STA để tấn công mục tiêu, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;. Trong thời gian ngắn sau khi thực hiện Đòn Nặng, dùng Đòn Cơ Bản để kích hoạt Giai Đoạn 4 Đòn Cơ Bản.</t>
         </is>
       </c>
     </row>
@@ -31536,7 +31536,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Rover: Hướng dẫn &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt;</t>
+          <t>Rover: Hướng dẫn &lt;color=#d4bf5f&gt;Đòn Tấn Công Mạnh&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -31601,7 +31601,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 5 đòn tấn công liên tiếp, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.</t>
+          <t>Thực hiện tối đa 5 đòn tấn công liên tiếp, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -31731,7 +31731,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Khi "Bóng Tối" đầy, giữ &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; để tung &lt;color=Highlight&gt;Devastation&lt;/color&gt;, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;, được tính là Sát Thương Heavy Attack. Sau khi tung &lt;color=Highlight&gt;Dark Surge&lt;/color&gt;, bước vào trạng thái &lt;color=Highlight&gt;Devastation&lt;/color&gt;. Trong trạng thái này: &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; sẽ được thay thế bằng đòn Basic Attack được tăng cường, thực hiện tối đa 5 đòn liên tiếp, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.</t>
+          <t>Khi "Bóng Tối" đầy, giữ &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt; để tung &lt;color=Highlight&gt;Tàn Phá&lt;/color&gt;, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;, được tính là Sát Thương Đòn Heavy Attack. Sau khi tung &lt;color=Highlight&gt;Tàn Phá&lt;/color&gt;, bước vào trạng thái &lt;color=Highlight&gt;Bùng Nổ Bóng Tối&lt;/color&gt;. Trong trạng thái này: &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt; sẽ được thay thế bằng đòn Basic Attack được tăng cường, thực hiện tối đa 5 đòn liên tiếp, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -31796,7 +31796,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Rover: &lt;color=#d4bf5f&gt;Forte Circuit&lt;/color&gt;</t>
+          <t>Rover: &lt;color=#d4bf5f&gt;Hướng dẫn Forte Circuit&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -31861,7 +31861,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Trong &lt;color=Highlight&gt;Dark Surge&lt;/color&gt;, sau khi dùng &lt;color=Highlight&gt;Basic Attack&lt;/color&gt;, dùng &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; để thi triển Heavy Attack Liên Hoàn lên mục tiêu, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;, được tính là Sát Thương Heavy Attack. Sau khi thi triển Heavy Attack Liên Hoàn, dùng &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; để thi triển Basic Attack 3 được tăng cường.</t>
+          <t>Trong &lt;color=Highlight&gt;Sóng Âm U Ám&lt;/color&gt;, sau khi dùng &lt;color=Highlight&gt;Đòn Heavy Attack&lt;/color&gt;, dùng &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt; để thi triển Đòn Heavy Attack Liên Hoàn lên mục tiêu, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;, được tính là Sát Thương Đòn Heavy Attack. Sau khi thi triển Đòn Heavy Attack Liên Hoàn, dùng &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt; để thi triển Đòn Basic Attack 3 được tăng cường.</t>
         </is>
       </c>
     </row>
@@ -31926,7 +31926,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Rover: Hướng dẫn &lt;color=#d4bf5f&gt;Forte Circuit&lt;/color&gt;: Heavy Attack</t>
+          <t>Rover: &lt;color=#d4bf5f&gt;Forte Circuit&lt;/color&gt; Tutorial: Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -31991,7 +31991,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Âm thanh kết tinh thành lưỡi kiếm, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.</t>
+          <t>Âm thanh kết tinh thành lưỡi kiếm, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -32056,7 +32056,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Rover: Hướng dẫn &lt;color=#d4bf5f&gt;Forte Circuit&lt;/color&gt;: Resonance Skill</t>
+          <t>Rover: &lt;color=#d4bf5f&gt;Forte Circuit&lt;/color&gt; Tutorial: Resonance Skill</t>
         </is>
       </c>
     </row>
@@ -32121,7 +32121,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Tập trung âm thanh trong lòng bàn tay để tấn công mục tiêu phía trước, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.</t>
+          <t>Tập trung âm thanh trong lòng bàn tay để tấn công mục tiêu phía trước, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -32251,7 +32251,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -32316,7 +32316,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Kỹ Năng Chain</t>
+          <t>Kỹ Năng Dây Xích</t>
         </is>
       </c>
     </row>
@@ -32448,9 +32448,9 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-Sau khi tung ra &lt;color=Highlight&gt;Basic Attack Stage 4&lt;/color&gt;, Changli bước vào trạng thái &lt;color=Highlight&gt;True Sight&lt;/color&gt;, kéo dài trong 12 giây.
-Khi ở trạng thái &lt;color=Highlight&gt;True Sight&lt;/color&gt;, nếu Changli sử dụng &lt;color=Highlight&gt;Ground Basic Attack&lt;/color&gt;, cô sẽ tung ra &lt;color=Highlight&gt;True Sight: Conquest&lt;/color&gt;, nhanh chóng tiếp cận kẻ địch và gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;, được tính là Sát Thương Resonance Skill. Khi gây sát thương, Changli nhận được 1 tầng [Enflamement]. Sau khi tung ra &lt;color=Highlight&gt;True Sight: Conquest&lt;/color&gt;, trạng thái &lt;color=Highlight&gt;True Sight&lt;/color&gt; sẽ kết thúc.</t>
+          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
+Sau khi tung ra &lt;color=Highlight&gt;Giai Đoạn Basic Attack 4&lt;/color&gt;, Changli bước vào trạng thái &lt;color=Highlight&gt;Chân Tướng&lt;/color&gt;, kéo dài trong 12 giây.
+Khi ở trạng thái &lt;color=Highlight&gt;Chân Tướng&lt;/color&gt;, nếu Changli sử dụng &lt;color=Highlight&gt;Basic Attack Trên Mặt Đất&lt;/color&gt;, cô sẽ tung ra &lt;color=Highlight&gt;Chân Tướng: Chinh Phục&lt;/color&gt;, nhanh chóng tiếp cận kẻ địch và gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;, được tính là Sát Thương Resonance Skill. Khi gây DMG, Changli nhận được 1 tầng [Enflamement]. Sau khi tung ra &lt;color=Highlight&gt;Chân Tướng: Chinh Phục&lt;/color&gt;, trạng thái &lt;color=Highlight&gt;Chân Tướng&lt;/color&gt; sẽ kết thúc.</t>
         </is>
       </c>
     </row>
@@ -32515,7 +32515,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Changli: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Changli: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -32582,9 +32582,9 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-Sau khi tung ra &lt;color=Highlight&gt;Basic Attack Stage 4&lt;/color&gt;, Changli bước vào trạng thái &lt;color=Highlight&gt;True Sight&lt;/color&gt;, kéo dài trong 12 giây.
-Khi ở trạng thái &lt;color=Highlight&gt;True Sight&lt;/color&gt;, nếu Changli &lt;color=Highlight&gt;jumps&lt;/color&gt; hoặc sử dụng &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; giữa không trung, cô sẽ tung ra &lt;color=Highlight&gt;True Sight: Charge&lt;/color&gt;, lao về phía kẻ địch và gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;, được tính là Sát Thương Resonance Skill. Khi gây sát thương, Changli nhận được 1 tầng [Enflamement]. Sau khi tung ra &lt;color=Highlight&gt;True Sight: Charge&lt;/color&gt;, trạng thái &lt;color=Highlight&gt;True Sight&lt;/color&gt; sẽ kết thúc.</t>
+          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
+Sau khi tung ra &lt;color=Highlight&gt;Giai Đoạn Basic Attack 4&lt;/color&gt;, Changli bước vào trạng thái &lt;color=Highlight&gt;Chân Tướng&lt;/color&gt;, kéo dài trong 12 giây.
+Khi ở trạng thái &lt;color=Highlight&gt;Chân Tướng&lt;/color&gt;, nếu Changli &lt;color=Highlight&gt;nhảy&lt;/color&gt; hoặc sử dụng &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; giữa không trung, cô sẽ tung ra &lt;color=Highlight&gt;Chân Tướng: Xung Phong&lt;/color&gt;, lao về phía kẻ địch và gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;, được tính là Sát Thương Resonance Skill. Khi gây DMG, Changli nhận được 1 tầng [Enflamement]. Sau khi tung ra &lt;color=Highlight&gt;Chân Tướng: Xung Phong&lt;/color&gt;, trạng thái &lt;color=Highlight&gt;Chân Tướng&lt;/color&gt; sẽ kết thúc.</t>
         </is>
       </c>
     </row>
@@ -32649,7 +32649,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Changli: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Changli: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -32714,7 +32714,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Sau khi giải phóng &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt;, Changli tấn công kẻ địch liên tiếp và bước vào trạng thái &lt;color=Highlight&gt;True Sight&lt;/color&gt;, kéo dài 12 giây. Cuối cùng, Changli tung ra một đòn tấn công bổ nhào, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Sau khi giải phóng &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt;, Changli tấn công kẻ địch liên tiếp và bước vào trạng thái &lt;color=Highlight&gt;Chân Nhãn&lt;/color&gt;, kéo dài 12 giây. Cuối cùng, Changli tung ra một đòn tấn công bổ nhào, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -32779,7 +32779,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Changli: &lt;color=#d4bf5f&gt;Resonance Skill&lt;/color&gt;</t>
+          <t>Changli: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Skill&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Sau khi giải phóng &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt;, Changli tấn công kẻ địch liên tiếp và bước vào trạng thái &lt;color=Highlight&gt;True Sight&lt;/color&gt;, kéo dài 12 giây. Cuối cùng, Changli tung ra một đòn tấn công bổ nhào, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Sau khi giải phóng &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt;, Changli tấn công kẻ địch liên tiếp và bước vào trạng thái &lt;color=Highlight&gt;Chân Nhãn&lt;/color&gt;, kéo dài 12 giây. Cuối cùng, Changli tung ra một đòn tấn công bổ nhào, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -32909,7 +32909,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Changli: &lt;color=#d4bf5f&gt;Resonance Skill&lt;/color&gt;</t>
+          <t>Changli: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Skill&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -33040,8 +33040,8 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để thực hiện tối đa 4 đòn tấn công liên tiếp trên không, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-Sau khi giải phóng &lt;color=Highlight&gt;Mid-air Attack Stage 4&lt;/color&gt;, Changli bước vào trạng thái &lt;color=Highlight&gt;True Sight&lt;/color&gt;, kéo dài trong 12 giây.</t>
+          <t>Tiêu hao STA để thực hiện tối đa 4 đòn tấn công liên tiếp trên không, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
+Sau khi giải phóng &lt;color=Highlight&gt;Giai Đoạn Mid-air Attack 4&lt;/color&gt;, Changli bước vào trạng thái &lt;color=Highlight&gt;Thị Giác Chân Thực&lt;/color&gt;, kéo dài trong 12 giây.</t>
         </is>
       </c>
     </row>
@@ -33106,7 +33106,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Giữ &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; trên mặt đất để tiêu hao STA, tung đòn đánh bay lên, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;. Trong khoảng thời gian nhất định, sử dụng &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; để tung ra &lt;color=Highlight&gt;Mid-air Attack Stage 3&lt;/color&gt;.</t>
+          <t>Giữ &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt; trên mặt đất để tiêu hao STA, tung đòn đánh bay lên, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;. Trong khoảng thời gian nhất định, sử dụng &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt; để tung ra &lt;color=Highlight&gt;Đòn Tấn Công Giữa Không Trọng P3&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -33171,7 +33171,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Changli: &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt;</t>
+          <t>Changli: &lt;color=#d4bf5f&gt;Hướng dẫn Heavy Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
